--- a/Erettsegi_Adatok/Irodalom/irodalom-osszes-mu-tablazat.xlsx
+++ b/Erettsegi_Adatok/Irodalom/irodalom-osszes-mu-tablazat.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programozás\Gyakorlás\Web\Erettsegi\adatok\irodalom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programozás\Gyakorlás\Web\Erettsegi-v2\Erettsegi_Adatok\Irodalom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43679AD-70D9-4C59-899A-C4D59B0F0C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE3CFFF-A251-43B3-90ED-C31FAFC7EE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6029,17 +6029,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I1003"/>
+  <dimension ref="A1:G1003"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="26.140625" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" customWidth="1"/>
-    <col min="4" max="4" width="30.42578125" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="142.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="48.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6062,7 +6063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -6073,7 +6074,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" ht="12.75">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -6096,7 +6097,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" ht="12.75">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6119,7 +6120,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="12.75">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -6142,7 +6143,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="12.75">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -6165,7 +6166,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" ht="12.75">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -6188,7 +6189,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" ht="12.75">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -6211,7 +6212,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" ht="12.75">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
@@ -6234,7 +6235,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" ht="12.75">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -6257,7 +6258,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" ht="12.75">
       <c r="A11" s="1" t="s">
         <v>54</v>
       </c>
@@ -6280,7 +6281,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" ht="12.75">
       <c r="A12" s="1" t="s">
         <v>65</v>
       </c>
@@ -6303,7 +6304,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" ht="12.75">
       <c r="A13" s="1" t="s">
         <v>71</v>
       </c>
@@ -6326,7 +6327,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" ht="12.75">
       <c r="A14" s="1" t="s">
         <v>76</v>
       </c>
@@ -6349,7 +6350,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" ht="12.75">
       <c r="A15" s="1" t="s">
         <v>83</v>
       </c>
@@ -6372,7 +6373,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" ht="12.75">
       <c r="A16" s="1" t="s">
         <v>87</v>
       </c>
@@ -6395,7 +6396,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" ht="12.75">
       <c r="A17" s="1" t="s">
         <v>93</v>
       </c>
@@ -6418,7 +6419,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" ht="12.75">
       <c r="A18" s="1" t="s">
         <v>100</v>
       </c>
@@ -6441,7 +6442,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" ht="12.75">
       <c r="A19" s="1" t="s">
         <v>100</v>
       </c>
@@ -6464,7 +6465,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" ht="12.75">
       <c r="A20" s="1" t="s">
         <v>110</v>
       </c>
@@ -6487,7 +6488,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" ht="12.75">
       <c r="A21" s="1" t="s">
         <v>116</v>
       </c>
@@ -6510,7 +6511,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" ht="12.75">
       <c r="A22" s="1" t="s">
         <v>116</v>
       </c>
@@ -6533,7 +6534,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" ht="12.75">
       <c r="A23" s="1" t="s">
         <v>127</v>
       </c>
@@ -6556,7 +6557,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" ht="12.75">
       <c r="A24" s="1" t="s">
         <v>127</v>
       </c>
@@ -6579,7 +6580,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" ht="12.75">
       <c r="A25" s="1" t="s">
         <v>137</v>
       </c>
@@ -6602,7 +6603,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" ht="12.75">
       <c r="A26" s="1" t="s">
         <v>137</v>
       </c>
@@ -6625,7 +6626,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" ht="12.75">
       <c r="A27" s="1" t="s">
         <v>146</v>
       </c>
@@ -6645,7 +6646,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" ht="12.75">
       <c r="A28" s="1" t="s">
         <v>146</v>
       </c>
@@ -6665,7 +6666,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" ht="12.75">
       <c r="A29" s="1" t="s">
         <v>156</v>
       </c>
@@ -6688,7 +6689,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" ht="12.75">
       <c r="A30" s="1" t="s">
         <v>162</v>
       </c>
@@ -6711,7 +6712,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" ht="12.75">
       <c r="A31" s="1" t="s">
         <v>162</v>
       </c>
@@ -6734,7 +6735,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" ht="12.75">
       <c r="A32" s="1" t="s">
         <v>162</v>
       </c>
@@ -6757,7 +6758,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" ht="12.75">
       <c r="A33" s="1" t="s">
         <v>172</v>
       </c>
@@ -6780,7 +6781,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" ht="12.75">
       <c r="A34" s="1" t="s">
         <v>172</v>
       </c>
@@ -6803,7 +6804,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" ht="12.75">
       <c r="A35" s="1" t="s">
         <v>172</v>
       </c>
@@ -6826,7 +6827,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" ht="12.75">
       <c r="A36" s="1" t="s">
         <v>185</v>
       </c>
@@ -6849,7 +6850,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" ht="12.75">
       <c r="A37" s="1" t="s">
         <v>191</v>
       </c>
@@ -6872,7 +6873,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" ht="12.75">
       <c r="A38" s="1" t="s">
         <v>191</v>
       </c>
@@ -6895,7 +6896,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" ht="12.75">
       <c r="A39" s="1" t="s">
         <v>200</v>
       </c>
@@ -6918,7 +6919,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" ht="12.75">
       <c r="A40" s="1" t="s">
         <v>200</v>
       </c>
@@ -6941,7 +6942,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" ht="12.75">
       <c r="A41" s="1" t="s">
         <v>200</v>
       </c>
@@ -6964,7 +6965,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" ht="12.75">
       <c r="A42" s="1" t="s">
         <v>211</v>
       </c>
@@ -6987,7 +6988,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" ht="12.75">
       <c r="A43" s="1" t="s">
         <v>211</v>
       </c>
@@ -7010,7 +7011,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" ht="12.75">
       <c r="A44" s="1" t="s">
         <v>211</v>
       </c>
@@ -7033,7 +7034,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" ht="12.75">
       <c r="A45" s="1" t="s">
         <v>222</v>
       </c>
@@ -7056,7 +7057,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" ht="12.75">
       <c r="A46" s="1" t="s">
         <v>229</v>
       </c>
@@ -7079,7 +7080,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" ht="12.75">
       <c r="A47" s="1" t="s">
         <v>235</v>
       </c>
@@ -7102,7 +7103,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" ht="12.75">
       <c r="A48" s="1" t="s">
         <v>235</v>
       </c>
@@ -7125,7 +7126,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" ht="12.75">
       <c r="A49" s="1" t="s">
         <v>235</v>
       </c>
@@ -7148,7 +7149,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" ht="12.75">
       <c r="A50" s="1" t="s">
         <v>235</v>
       </c>
@@ -7171,7 +7172,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" ht="12.75">
       <c r="A51" s="1" t="s">
         <v>250</v>
       </c>
@@ -7194,7 +7195,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" ht="12.75">
       <c r="A52" s="1" t="s">
         <v>250</v>
       </c>
@@ -7217,7 +7218,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" ht="12.75">
       <c r="A53" s="1" t="s">
         <v>250</v>
       </c>
@@ -7240,7 +7241,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" ht="12.75">
       <c r="A54" s="1" t="s">
         <v>262</v>
       </c>
@@ -7263,7 +7264,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" ht="12.75">
       <c r="A55" s="1" t="s">
         <v>262</v>
       </c>
@@ -7286,7 +7287,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" ht="12.75">
       <c r="A56" s="1" t="s">
         <v>262</v>
       </c>
@@ -7309,7 +7310,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" ht="12.75">
       <c r="A57" s="1" t="s">
         <v>110</v>
       </c>
@@ -7332,7 +7333,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" ht="12.75">
       <c r="A58" s="1" t="s">
         <v>277</v>
       </c>
@@ -7355,7 +7356,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" ht="12.75">
       <c r="A59" s="1" t="s">
         <v>277</v>
       </c>
@@ -7378,7 +7379,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" ht="12.75">
       <c r="A60" s="1" t="s">
         <v>277</v>
       </c>
@@ -7401,7 +7402,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" ht="12.75">
       <c r="A61" s="1" t="s">
         <v>277</v>
       </c>
@@ -7424,7 +7425,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" ht="12.75">
       <c r="A62" s="1" t="s">
         <v>277</v>
       </c>
@@ -7447,7 +7448,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" ht="12.75">
       <c r="A63" s="1" t="s">
         <v>277</v>
       </c>
@@ -7470,7 +7471,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" ht="12.75">
       <c r="A64" s="1" t="s">
         <v>306</v>
       </c>
@@ -7493,7 +7494,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" ht="12.75">
       <c r="A65" s="1" t="s">
         <v>312</v>
       </c>
@@ -7516,7 +7517,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" ht="12.75">
       <c r="A66" s="1" t="s">
         <v>277</v>
       </c>
@@ -7539,7 +7540,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" ht="12.75">
       <c r="A67" s="1" t="s">
         <v>277</v>
       </c>
@@ -7562,7 +7563,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" ht="12.75">
       <c r="A68" s="1" t="s">
         <v>277</v>
       </c>
@@ -7585,7 +7586,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" ht="12.75">
       <c r="A69" s="1" t="s">
         <v>277</v>
       </c>
@@ -7608,7 +7609,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" ht="12.75">
       <c r="A70" s="1" t="s">
         <v>277</v>
       </c>
@@ -7631,7 +7632,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" ht="12.75">
       <c r="A71" s="1" t="s">
         <v>277</v>
       </c>
@@ -7654,7 +7655,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" ht="12.75">
       <c r="A72" s="1" t="s">
         <v>277</v>
       </c>
@@ -7677,7 +7678,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" ht="12.75">
       <c r="A73" s="1" t="s">
         <v>116</v>
       </c>
@@ -7700,7 +7701,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" ht="12.75">
       <c r="A74" s="1" t="s">
         <v>8</v>
       </c>
@@ -7723,7 +7724,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" ht="12.75">
       <c r="A75" s="1" t="s">
         <v>355</v>
       </c>
@@ -7746,7 +7747,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" ht="12.75">
       <c r="A76" s="1" t="s">
         <v>362</v>
       </c>
@@ -7769,7 +7770,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" ht="12.75">
       <c r="A77" s="1" t="s">
         <v>366</v>
       </c>
@@ -7792,7 +7793,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" ht="12.75">
       <c r="A78" s="1" t="s">
         <v>373</v>
       </c>
@@ -7815,7 +7816,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" ht="12.75">
       <c r="A79" s="1" t="s">
         <v>116</v>
       </c>
@@ -7838,7 +7839,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" ht="12.75">
       <c r="A80" s="1" t="s">
         <v>116</v>
       </c>
@@ -7861,7 +7862,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" ht="12.75">
       <c r="A81" s="1" t="s">
         <v>116</v>
       </c>
@@ -7884,7 +7885,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" ht="12.75">
       <c r="A82" s="1" t="s">
         <v>116</v>
       </c>
@@ -7907,7 +7908,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" ht="12.75">
       <c r="A83" s="1" t="s">
         <v>400</v>
       </c>
@@ -7930,7 +7931,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" ht="12.75">
       <c r="A84" s="1" t="s">
         <v>405</v>
       </c>
@@ -7953,7 +7954,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" ht="12.75">
       <c r="A85" s="1" t="s">
         <v>116</v>
       </c>
@@ -7976,7 +7977,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" ht="12.75">
       <c r="A86" s="1" t="s">
         <v>415</v>
       </c>
@@ -7999,7 +8000,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" ht="12.75">
       <c r="A87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8022,7 +8023,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" ht="12.75">
       <c r="A88" s="1" t="s">
         <v>421</v>
       </c>
@@ -8045,7 +8046,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" ht="12.75">
       <c r="A89" s="1" t="s">
         <v>426</v>
       </c>
@@ -8068,7 +8069,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" ht="12.75">
       <c r="A90" s="1" t="s">
         <v>426</v>
       </c>
@@ -8091,7 +8092,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" ht="12.75">
       <c r="A91" s="1" t="s">
         <v>436</v>
       </c>
@@ -8114,7 +8115,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" ht="12.75">
       <c r="A92" s="1" t="s">
         <v>441</v>
       </c>
@@ -8137,7 +8138,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" ht="12.75">
       <c r="A93" s="1" t="s">
         <v>116</v>
       </c>
@@ -8160,7 +8161,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" ht="12.75">
       <c r="A94" s="1" t="s">
         <v>453</v>
       </c>
@@ -8183,7 +8184,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" ht="12.75">
       <c r="A95" s="1" t="s">
         <v>453</v>
       </c>
@@ -8206,7 +8207,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" ht="12.75">
       <c r="A96" s="1" t="s">
         <v>463</v>
       </c>
@@ -8229,7 +8230,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" ht="12.75">
       <c r="A97" s="1" t="s">
         <v>469</v>
       </c>
@@ -8252,7 +8253,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" ht="12.75">
       <c r="A98" s="1" t="s">
         <v>469</v>
       </c>
@@ -8275,7 +8276,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" ht="12.75">
       <c r="A99" s="1" t="s">
         <v>469</v>
       </c>
@@ -8298,7 +8299,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" ht="12.75">
       <c r="A100" s="1" t="s">
         <v>469</v>
       </c>
@@ -8321,7 +8322,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" ht="12.75">
       <c r="A101" s="1" t="s">
         <v>483</v>
       </c>
@@ -8344,7 +8345,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" ht="12.75">
       <c r="A102" s="1" t="s">
         <v>483</v>
       </c>
@@ -8367,7 +8368,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" ht="12.75">
       <c r="A103" s="1" t="s">
         <v>483</v>
       </c>
@@ -8390,7 +8391,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" ht="12.75">
       <c r="A104" s="1" t="s">
         <v>483</v>
       </c>
@@ -8413,7 +8414,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" ht="12.75">
       <c r="A105" s="1" t="s">
         <v>483</v>
       </c>
@@ -8436,7 +8437,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" ht="12.75">
       <c r="A106" s="1" t="s">
         <v>483</v>
       </c>
@@ -8459,7 +8460,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" ht="12.75">
       <c r="A107" s="1" t="s">
         <v>509</v>
       </c>
@@ -8482,7 +8483,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" ht="12.75">
       <c r="A108" s="1" t="s">
         <v>509</v>
       </c>
@@ -8505,7 +8506,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" ht="12.75">
       <c r="A109" s="1" t="s">
         <v>509</v>
       </c>
@@ -8528,15 +8529,15 @@
         <v>521</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" ht="12.75">
       <c r="A110" s="3"/>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" ht="12.75">
       <c r="A111" s="1" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" ht="12.75">
       <c r="A112" s="4" t="s">
         <v>523</v>
       </c>
@@ -8559,7 +8560,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" ht="12.75">
       <c r="A113" s="4" t="s">
         <v>529</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" ht="12.75">
       <c r="A114" s="4" t="s">
         <v>534</v>
       </c>
@@ -8605,7 +8606,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" ht="12.75">
       <c r="A115" s="4" t="s">
         <v>541</v>
       </c>
@@ -8628,7 +8629,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" ht="12.75">
       <c r="A116" s="4" t="s">
         <v>546</v>
       </c>
@@ -8651,7 +8652,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" ht="12.75">
       <c r="A117" s="4" t="s">
         <v>552</v>
       </c>
@@ -8674,7 +8675,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" ht="12.75">
       <c r="A118" s="4" t="s">
         <v>556</v>
       </c>
@@ -8697,7 +8698,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" ht="12.75">
       <c r="A119" s="4" t="s">
         <v>561</v>
       </c>
@@ -8720,7 +8721,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" ht="12.75">
       <c r="A120" s="4" t="s">
         <v>567</v>
       </c>
@@ -8743,7 +8744,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" ht="12.75">
       <c r="A121" s="4" t="s">
         <v>573</v>
       </c>
@@ -8766,7 +8767,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" ht="12.75">
       <c r="A122" s="4" t="s">
         <v>579</v>
       </c>
@@ -8789,7 +8790,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" ht="12.75">
       <c r="A123" s="4" t="s">
         <v>579</v>
       </c>
@@ -8812,7 +8813,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" ht="12.75">
       <c r="A124" s="4" t="s">
         <v>579</v>
       </c>
@@ -8835,7 +8836,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" ht="12.75">
       <c r="A125" s="4" t="s">
         <v>579</v>
       </c>
@@ -8858,7 +8859,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" ht="12.75">
       <c r="A126" s="4" t="s">
         <v>579</v>
       </c>
@@ -8881,7 +8882,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" ht="12.75">
       <c r="A127" s="4" t="s">
         <v>579</v>
       </c>
@@ -8904,7 +8905,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" ht="12.75">
       <c r="A128" s="4" t="s">
         <v>579</v>
       </c>
@@ -8927,7 +8928,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" ht="12.75">
       <c r="A129" s="4" t="s">
         <v>579</v>
       </c>
@@ -8950,7 +8951,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" ht="12.75">
       <c r="A130" s="4" t="s">
         <v>612</v>
       </c>
@@ -8973,7 +8974,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" ht="12.75">
       <c r="A131" s="4" t="s">
         <v>617</v>
       </c>
@@ -8996,7 +8997,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" ht="12.75">
       <c r="A132" s="4" t="s">
         <v>623</v>
       </c>
@@ -9019,7 +9020,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" ht="12.75">
       <c r="A133" s="4" t="s">
         <v>629</v>
       </c>
@@ -9042,7 +9043,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" ht="12.75">
       <c r="A134" s="4" t="s">
         <v>629</v>
       </c>
@@ -9065,7 +9066,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" ht="12.75">
       <c r="A135" s="4" t="s">
         <v>638</v>
       </c>
@@ -9088,7 +9089,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" ht="12.75">
       <c r="A136" s="4" t="s">
         <v>645</v>
       </c>
@@ -9157,7 +9158,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" ht="12.75">
       <c r="A139" s="4" t="s">
         <v>655</v>
       </c>
@@ -9180,7 +9181,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" ht="12.75">
       <c r="A140" s="4" t="s">
         <v>655</v>
       </c>
@@ -9203,7 +9204,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" ht="12.75">
       <c r="A141" s="4" t="s">
         <v>655</v>
       </c>
@@ -9295,7 +9296,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="12.75">
+    <row r="145" spans="1:7" ht="12.75">
       <c r="A145" s="4" t="s">
         <v>690</v>
       </c>
@@ -9318,7 +9319,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="12.75">
+    <row r="146" spans="1:7" ht="12.75">
       <c r="A146" s="4" t="s">
         <v>696</v>
       </c>
@@ -9341,7 +9342,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="12.75">
+    <row r="147" spans="1:7" ht="12.75">
       <c r="A147" s="4" t="s">
         <v>702</v>
       </c>
@@ -9364,7 +9365,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="12.75">
+    <row r="148" spans="1:7" ht="12.75">
       <c r="A148" s="4" t="s">
         <v>1859</v>
       </c>
@@ -9387,7 +9388,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="12.75">
+    <row r="149" spans="1:7" ht="12.75">
       <c r="A149" s="4" t="s">
         <v>1864</v>
       </c>
@@ -9409,10 +9410,8 @@
       <c r="G149" t="s">
         <v>1868</v>
       </c>
-      <c r="H149" s="11"/>
-      <c r="I149" s="11"/>
-    </row>
-    <row r="150" spans="1:9" ht="12.75">
+    </row>
+    <row r="150" spans="1:7" ht="12.75">
       <c r="A150" s="4" t="s">
         <v>708</v>
       </c>
@@ -9435,7 +9434,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:7" ht="12.75">
       <c r="A151" s="4" t="s">
         <v>708</v>
       </c>
@@ -9458,7 +9457,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:7" ht="12.75">
       <c r="A152" s="4" t="s">
         <v>708</v>
       </c>
@@ -9481,7 +9480,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:7" ht="12.75">
       <c r="A153" s="4" t="s">
         <v>722</v>
       </c>
@@ -9504,7 +9503,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:7" ht="12.75">
       <c r="A154" s="4" t="s">
         <v>722</v>
       </c>
@@ -9527,7 +9526,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:7" ht="12.75">
       <c r="A155" s="4" t="s">
         <v>722</v>
       </c>
@@ -9550,7 +9549,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:7" ht="12.75">
       <c r="A156" s="4" t="s">
         <v>734</v>
       </c>
@@ -9573,7 +9572,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:7" ht="12.75">
       <c r="A157" s="4" t="s">
         <v>734</v>
       </c>
@@ -9596,7 +9595,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:7" ht="12.75">
       <c r="A158" s="4" t="s">
         <v>742</v>
       </c>
@@ -9619,7 +9618,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:7" ht="12.75">
       <c r="A159" s="4" t="s">
         <v>742</v>
       </c>
@@ -9642,7 +9641,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:7" ht="12.75">
       <c r="A160" s="4" t="s">
         <v>752</v>
       </c>
@@ -9665,7 +9664,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" ht="12.75">
       <c r="A161" s="4" t="s">
         <v>752</v>
       </c>
@@ -9688,7 +9687,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" ht="12.75">
       <c r="A162" s="4" t="s">
         <v>763</v>
       </c>
@@ -9711,7 +9710,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" ht="12.75">
       <c r="A163" s="4" t="s">
         <v>763</v>
       </c>
@@ -9734,7 +9733,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" ht="12.75">
       <c r="A164" s="4" t="s">
         <v>763</v>
       </c>
@@ -9757,7 +9756,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" ht="12.75">
       <c r="A165" s="4" t="s">
         <v>763</v>
       </c>
@@ -9780,7 +9779,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" ht="12.75">
       <c r="A166" s="4" t="s">
         <v>763</v>
       </c>
@@ -9803,7 +9802,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" ht="12.75">
       <c r="A167" s="4" t="s">
         <v>763</v>
       </c>
@@ -9826,7 +9825,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" ht="12.75">
       <c r="A168" s="4" t="s">
         <v>763</v>
       </c>
@@ -9849,7 +9848,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" ht="12.75">
       <c r="A169" s="4" t="s">
         <v>763</v>
       </c>
@@ -9872,7 +9871,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" ht="12.75">
       <c r="A170" s="4" t="s">
         <v>763</v>
       </c>
@@ -9895,7 +9894,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" ht="12.75">
       <c r="A171" s="4" t="s">
         <v>763</v>
       </c>
@@ -9918,7 +9917,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" ht="12.75">
       <c r="A172" s="4" t="s">
         <v>763</v>
       </c>
@@ -9941,7 +9940,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" ht="12.75">
       <c r="A173" s="4" t="s">
         <v>763</v>
       </c>
@@ -9964,7 +9963,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" ht="12.75">
       <c r="A174" s="4" t="s">
         <v>763</v>
       </c>
@@ -9987,7 +9986,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" ht="12.75">
       <c r="A175" s="4" t="s">
         <v>763</v>
       </c>
@@ -10010,7 +10009,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" ht="12.75">
       <c r="A176" s="4" t="s">
         <v>763</v>
       </c>
@@ -10033,7 +10032,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" ht="12.75">
       <c r="A177" s="4" t="s">
         <v>824</v>
       </c>
@@ -10056,7 +10055,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" ht="12.75">
       <c r="A178" s="4" t="s">
         <v>824</v>
       </c>
@@ -10079,7 +10078,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" ht="12.75">
       <c r="A179" s="4" t="s">
         <v>824</v>
       </c>
@@ -10102,7 +10101,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" ht="12.75">
       <c r="A180" s="4" t="s">
         <v>824</v>
       </c>
@@ -10125,7 +10124,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" ht="12.75">
       <c r="A181" s="4" t="s">
         <v>824</v>
       </c>
@@ -10148,7 +10147,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" ht="12.75">
       <c r="A182" s="4" t="s">
         <v>824</v>
       </c>
@@ -10171,7 +10170,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" ht="12.75">
       <c r="A183" s="4" t="s">
         <v>824</v>
       </c>
@@ -10194,7 +10193,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" ht="12.75">
       <c r="A184" s="4" t="s">
         <v>824</v>
       </c>
@@ -10217,7 +10216,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" ht="12.75">
       <c r="A185" s="4" t="s">
         <v>824</v>
       </c>
@@ -10240,7 +10239,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" ht="12.75">
       <c r="A186" s="4" t="s">
         <v>824</v>
       </c>
@@ -10263,7 +10262,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" ht="12.75">
       <c r="A187" s="4" t="s">
         <v>862</v>
       </c>
@@ -10286,7 +10285,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" ht="12.75">
       <c r="A188" s="4" t="s">
         <v>862</v>
       </c>
@@ -10309,7 +10308,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" ht="12.75">
       <c r="A189" s="4" t="s">
         <v>306</v>
       </c>
@@ -10332,7 +10331,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" ht="12.75">
       <c r="A190" s="4" t="s">
         <v>306</v>
       </c>
@@ -10355,7 +10354,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" ht="12.75">
       <c r="A191" s="4" t="s">
         <v>306</v>
       </c>
@@ -10378,7 +10377,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" ht="12.75">
       <c r="A192" s="4" t="s">
         <v>306</v>
       </c>
@@ -10401,7 +10400,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:7" ht="12.75">
       <c r="A193" s="4" t="s">
         <v>306</v>
       </c>
@@ -10424,7 +10423,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" ht="12.75">
       <c r="A194" s="4" t="s">
         <v>306</v>
       </c>
@@ -10447,7 +10446,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" spans="1:7" ht="12.75">
       <c r="A195" s="4" t="s">
         <v>306</v>
       </c>
@@ -10470,7 +10469,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" spans="1:7" ht="12.75">
       <c r="A196" s="4" t="s">
         <v>306</v>
       </c>
@@ -10493,7 +10492,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:7" ht="12.75">
       <c r="A197" s="4" t="s">
         <v>306</v>
       </c>
@@ -10516,7 +10515,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" spans="1:7" ht="12.75">
       <c r="A198" s="4" t="s">
         <v>904</v>
       </c>
@@ -10539,7 +10538,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" spans="1:7" ht="12.75">
       <c r="A199" s="4" t="s">
         <v>910</v>
       </c>
@@ -10562,7 +10561,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" spans="1:7" ht="12.75">
       <c r="A200" s="4" t="s">
         <v>917</v>
       </c>
@@ -10585,7 +10584,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" spans="1:7" ht="12.75">
       <c r="A201" s="4" t="s">
         <v>922</v>
       </c>
@@ -10608,7 +10607,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" spans="1:7" ht="12.75">
       <c r="A202" s="4" t="s">
         <v>922</v>
       </c>
@@ -10631,7 +10630,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" spans="1:7" ht="12.75">
       <c r="A203" s="4" t="s">
         <v>931</v>
       </c>
@@ -10654,7 +10653,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" spans="1:7" ht="12.75">
       <c r="A204" s="4" t="s">
         <v>936</v>
       </c>
@@ -10677,7 +10676,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" ht="12.75">
       <c r="A205" s="4" t="s">
         <v>941</v>
       </c>
@@ -10700,7 +10699,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" spans="1:7" ht="12.75">
       <c r="A206" s="4" t="s">
         <v>941</v>
       </c>
@@ -10723,7 +10722,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" spans="1:7" ht="12.75">
       <c r="A207" s="4" t="s">
         <v>941</v>
       </c>
@@ -10746,7 +10745,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" spans="1:7" ht="12.75">
       <c r="A208" s="4" t="s">
         <v>953</v>
       </c>
@@ -10769,7 +10768,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" ht="12.75">
       <c r="A209" s="4" t="s">
         <v>960</v>
       </c>
@@ -10792,7 +10791,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:7" ht="12.75">
       <c r="A210" s="4" t="s">
         <v>965</v>
       </c>
@@ -10815,7 +10814,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:7" ht="12.75">
       <c r="A211" s="4" t="s">
         <v>965</v>
       </c>
@@ -10838,7 +10837,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" ht="12.75">
       <c r="A212" s="4" t="s">
         <v>965</v>
       </c>
@@ -10861,7 +10860,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:7" ht="12.75">
       <c r="A213" s="4" t="s">
         <v>965</v>
       </c>
@@ -10884,7 +10883,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:7" ht="12.75">
       <c r="A214" s="4" t="s">
         <v>965</v>
       </c>
@@ -10907,7 +10906,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" ht="12.75">
       <c r="A215" s="4" t="s">
         <v>965</v>
       </c>
@@ -10930,7 +10929,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:7" ht="12.75">
       <c r="A216" s="4" t="s">
         <v>965</v>
       </c>
@@ -10953,7 +10952,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:7" ht="12.75">
       <c r="A217" s="4" t="s">
         <v>965</v>
       </c>
@@ -10976,7 +10975,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" spans="1:7" ht="12.75">
       <c r="A218" s="4" t="s">
         <v>999</v>
       </c>
@@ -10999,7 +10998,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" ht="12.75">
       <c r="A219" s="4" t="s">
         <v>999</v>
       </c>
@@ -11022,7 +11021,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" ht="12.75">
       <c r="A220" s="4" t="s">
         <v>999</v>
       </c>
@@ -11045,7 +11044,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" ht="12.75">
       <c r="A221" s="4" t="s">
         <v>999</v>
       </c>
@@ -11068,7 +11067,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" ht="12.75">
       <c r="A222" s="4" t="s">
         <v>999</v>
       </c>
@@ -11091,7 +11090,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" ht="12.75">
       <c r="A223" s="4" t="s">
         <v>999</v>
       </c>
@@ -11114,7 +11113,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" ht="12.75">
       <c r="A224" s="4" t="s">
         <v>999</v>
       </c>
@@ -11137,7 +11136,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" ht="12.75">
       <c r="A225" s="4" t="s">
         <v>999</v>
       </c>
@@ -11160,7 +11159,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:7" ht="12.75">
       <c r="A226" s="4" t="s">
         <v>999</v>
       </c>
@@ -11183,7 +11182,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" ht="12.75">
       <c r="A227" s="4" t="s">
         <v>999</v>
       </c>
@@ -11206,7 +11205,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:7" ht="12.75">
       <c r="A228" s="4" t="s">
         <v>999</v>
       </c>
@@ -11229,7 +11228,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" ht="12.75">
       <c r="A229" s="4" t="s">
         <v>999</v>
       </c>
@@ -11252,7 +11251,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" spans="1:7" ht="12.75">
       <c r="A230" s="4" t="s">
         <v>999</v>
       </c>
@@ -11275,7 +11274,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" spans="1:7" ht="12.75">
       <c r="A231" s="4" t="s">
         <v>999</v>
       </c>
@@ -11298,7 +11297,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" spans="1:7" ht="12.75">
       <c r="A232" s="4" t="s">
         <v>999</v>
       </c>
@@ -11321,7 +11320,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" spans="1:7" ht="12.75">
       <c r="A233" s="4" t="s">
         <v>999</v>
       </c>
@@ -11344,7 +11343,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" spans="1:7" ht="12.75">
       <c r="A234" s="4" t="s">
         <v>999</v>
       </c>
@@ -11367,7 +11366,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" spans="1:7" ht="12.75">
       <c r="A235" s="4" t="s">
         <v>999</v>
       </c>
@@ -11390,7 +11389,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" spans="1:7" ht="12.75">
       <c r="A236" s="4" t="s">
         <v>999</v>
       </c>
@@ -11413,7 +11412,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" spans="1:7" ht="12.75">
       <c r="A237" s="4" t="s">
         <v>999</v>
       </c>
@@ -11436,7 +11435,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" spans="1:7" ht="12.75">
       <c r="A238" s="4" t="s">
         <v>999</v>
       </c>
@@ -11459,7 +11458,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" spans="1:7" ht="12.75">
       <c r="A239" s="4" t="s">
         <v>999</v>
       </c>
@@ -11482,7 +11481,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" spans="1:7" ht="12.75">
       <c r="A240" s="4" t="s">
         <v>999</v>
       </c>
@@ -11505,7 +11504,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:7" ht="12.75">
       <c r="A241" s="4" t="s">
         <v>1091</v>
       </c>
@@ -11528,7 +11527,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:7" ht="12.75">
       <c r="A242" s="4" t="s">
         <v>1091</v>
       </c>
@@ -11551,7 +11550,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:7" ht="12.75">
       <c r="A243" s="4" t="s">
         <v>1091</v>
       </c>
@@ -11574,7 +11573,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:7" ht="12.75">
       <c r="A244" s="4" t="s">
         <v>1091</v>
       </c>
@@ -11597,7 +11596,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" spans="1:7" ht="12.75">
       <c r="A245" s="4" t="s">
         <v>1108</v>
       </c>
@@ -11620,7 +11619,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" spans="1:7" ht="12.75">
       <c r="A246" s="4" t="s">
         <v>1113</v>
       </c>
@@ -11643,15 +11642,15 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:7" ht="12.75">
       <c r="A247" s="3"/>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" spans="1:7" ht="12.75">
       <c r="A248" s="1" t="s">
         <v>1119</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" spans="1:7" ht="12.75">
       <c r="A249" s="4" t="s">
         <v>1120</v>
       </c>
@@ -11674,7 +11673,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" spans="1:7" ht="12.75">
       <c r="A250" s="4" t="s">
         <v>1125</v>
       </c>
@@ -11697,7 +11696,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" spans="1:7" ht="12.75">
       <c r="A251" s="8" t="s">
         <v>1131</v>
       </c>
@@ -11720,7 +11719,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" spans="1:7" ht="12.75">
       <c r="A252" s="4" t="s">
         <v>1137</v>
       </c>
@@ -11743,7 +11742,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" spans="1:7" ht="12.75">
       <c r="A253" s="8" t="s">
         <v>1142</v>
       </c>
@@ -11766,7 +11765,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" spans="1:7" ht="12.75">
       <c r="A254" s="4" t="s">
         <v>1148</v>
       </c>
@@ -11789,7 +11788,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" spans="1:7" ht="12.75">
       <c r="A255" s="4" t="s">
         <v>1148</v>
       </c>
@@ -11812,7 +11811,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" spans="1:7" ht="12.75">
       <c r="A256" s="4" t="s">
         <v>1148</v>
       </c>
@@ -11835,7 +11834,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:7" ht="12.75">
       <c r="A257" s="4" t="s">
         <v>1148</v>
       </c>
@@ -11858,7 +11857,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:7" ht="12.75">
       <c r="A258" s="4" t="s">
         <v>1162</v>
       </c>
@@ -11881,7 +11880,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" spans="1:7" ht="12.75">
       <c r="A259" s="4" t="s">
         <v>1162</v>
       </c>
@@ -11904,7 +11903,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:7" ht="12.75">
       <c r="A260" s="4" t="s">
         <v>1162</v>
       </c>
@@ -11927,7 +11926,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:7" ht="12.75">
       <c r="A261" s="4" t="s">
         <v>1174</v>
       </c>
@@ -11950,7 +11949,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:7" ht="12.75">
       <c r="A262" s="4" t="s">
         <v>1174</v>
       </c>
@@ -11973,7 +11972,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:7" ht="12.75">
       <c r="A263" s="4" t="s">
         <v>1174</v>
       </c>
@@ -11996,7 +11995,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:7" ht="12.75">
       <c r="A264" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12019,7 +12018,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:7" ht="12.75">
       <c r="A265" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12042,7 +12041,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:7" ht="12.75">
       <c r="A266" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12065,7 +12064,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:7" ht="12.75">
       <c r="A267" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12088,7 +12087,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:7" ht="12.75">
       <c r="A268" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12111,7 +12110,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:7" ht="12.75">
       <c r="A269" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12134,7 +12133,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:7" ht="12.75">
       <c r="A270" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12157,7 +12156,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:7" ht="12.75">
       <c r="A271" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12180,7 +12179,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:7" ht="12.75">
       <c r="A272" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12203,7 +12202,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:7" ht="12.75">
       <c r="A273" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12226,7 +12225,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:7" ht="12.75">
       <c r="A274" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12249,7 +12248,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:7" ht="12.75">
       <c r="A275" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12272,7 +12271,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:7" ht="12.75">
       <c r="A276" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12295,7 +12294,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:7" ht="12.75">
       <c r="A277" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12318,7 +12317,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:7" ht="12.75">
       <c r="A278" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12341,7 +12340,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" spans="1:7" ht="12.75">
       <c r="A279" s="4" t="s">
         <v>1186</v>
       </c>
@@ -12364,7 +12363,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:7" ht="12.75">
       <c r="A280" s="4" t="s">
         <v>1248</v>
       </c>
@@ -12387,7 +12386,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" spans="1:7" ht="12.75">
       <c r="A281" s="4" t="s">
         <v>1248</v>
       </c>
@@ -12410,7 +12409,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" spans="1:7" ht="12.75">
       <c r="A282" s="4" t="s">
         <v>1248</v>
       </c>
@@ -12433,7 +12432,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:7" ht="12.75">
       <c r="A283" s="4" t="s">
         <v>1248</v>
       </c>
@@ -12456,7 +12455,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" spans="1:7" ht="12.75">
       <c r="A284" s="4" t="s">
         <v>1248</v>
       </c>
@@ -12479,7 +12478,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" spans="1:7" ht="12.75">
       <c r="A285" s="4" t="s">
         <v>1248</v>
       </c>
@@ -12502,7 +12501,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" spans="1:7" ht="12.75">
       <c r="A286" s="4" t="s">
         <v>1268</v>
       </c>
@@ -12525,7 +12524,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" spans="1:7" ht="12.75">
       <c r="A287" s="4" t="s">
         <v>1268</v>
       </c>
@@ -12548,7 +12547,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:7" ht="12.75">
       <c r="A288" s="4" t="s">
         <v>1277</v>
       </c>
@@ -12571,7 +12570,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" spans="1:7" ht="12.75">
       <c r="A289" s="4" t="s">
         <v>1277</v>
       </c>
@@ -12594,7 +12593,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" spans="1:7" ht="12.75">
       <c r="A290" s="4" t="s">
         <v>1287</v>
       </c>
@@ -12617,7 +12616,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" spans="1:7" ht="12.75">
       <c r="A291" s="4" t="s">
         <v>1287</v>
       </c>
@@ -12640,7 +12639,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" spans="1:7" ht="12.75">
       <c r="A292" s="4" t="s">
         <v>1287</v>
       </c>
@@ -12663,7 +12662,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" spans="1:7" ht="12.75">
       <c r="A293" s="4" t="s">
         <v>1302</v>
       </c>
@@ -12686,7 +12685,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" spans="1:7" ht="12.75">
       <c r="A294" s="4" t="s">
         <v>1302</v>
       </c>
@@ -12709,7 +12708,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" spans="1:7" ht="12.75">
       <c r="A295" s="4" t="s">
         <v>1310</v>
       </c>
@@ -12732,7 +12731,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" spans="1:7" ht="12.75">
       <c r="A296" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12755,7 +12754,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" spans="1:7" ht="12.75">
       <c r="A297" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12778,7 +12777,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" spans="1:7" ht="12.75">
       <c r="A298" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12801,7 +12800,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" spans="1:7" ht="12.75">
       <c r="A299" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12824,7 +12823,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" spans="1:7" ht="12.75">
       <c r="A300" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12847,7 +12846,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" spans="1:7" ht="12.75">
       <c r="A301" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12870,7 +12869,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" spans="1:7" ht="12.75">
       <c r="A302" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12893,7 +12892,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" spans="1:7" ht="12.75">
       <c r="A303" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12916,7 +12915,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" spans="1:7" ht="12.75">
       <c r="A304" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12939,7 +12938,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" spans="1:7" ht="12.75">
       <c r="A305" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12962,7 +12961,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" spans="1:7" ht="12.75">
       <c r="A306" s="4" t="s">
         <v>1316</v>
       </c>
@@ -12985,7 +12984,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" spans="1:7" ht="12.75">
       <c r="A307" s="4" t="s">
         <v>1316</v>
       </c>
@@ -13008,7 +13007,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" spans="1:7" ht="12.75">
       <c r="A308" s="4" t="s">
         <v>1316</v>
       </c>
@@ -13031,7 +13030,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="309" spans="1:7">
+    <row r="309" spans="1:7" ht="12.75">
       <c r="A309" s="4" t="s">
         <v>1316</v>
       </c>
@@ -13054,7 +13053,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" spans="1:7" ht="12.75">
       <c r="A310" s="4" t="s">
         <v>1316</v>
       </c>
@@ -13077,7 +13076,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" spans="1:7" ht="12.75">
       <c r="A311" s="4" t="s">
         <v>1316</v>
       </c>
@@ -13100,7 +13099,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" spans="1:7" ht="12.75">
       <c r="A312" s="4" t="s">
         <v>1316</v>
       </c>
@@ -13123,7 +13122,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" spans="1:7" ht="12.75">
       <c r="A313" s="4" t="s">
         <v>1316</v>
       </c>
@@ -13146,7 +13145,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" spans="1:7" ht="12.75">
       <c r="A314" s="4" t="s">
         <v>1316</v>
       </c>
@@ -13169,7 +13168,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" spans="1:7" ht="12.75">
       <c r="A315" s="4" t="s">
         <v>1316</v>
       </c>
@@ -13192,7 +13191,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="316" spans="1:7">
+    <row r="316" spans="1:7" ht="12.75">
       <c r="A316" s="4" t="s">
         <v>1316</v>
       </c>
@@ -13215,7 +13214,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" spans="1:7" ht="12.75">
       <c r="A317" s="4" t="s">
         <v>355</v>
       </c>
@@ -13238,7 +13237,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" spans="1:7" ht="12.75">
       <c r="A318" s="4" t="s">
         <v>355</v>
       </c>
@@ -13261,7 +13260,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" spans="1:7" ht="12.75">
       <c r="A319" s="4" t="s">
         <v>355</v>
       </c>
@@ -13284,7 +13283,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" spans="1:7" ht="12.75">
       <c r="A320" s="4" t="s">
         <v>355</v>
       </c>
@@ -13307,7 +13306,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" spans="1:7" ht="12.75">
       <c r="A321" s="4" t="s">
         <v>355</v>
       </c>
@@ -13330,7 +13329,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" spans="1:7" ht="12.75">
       <c r="A322" s="4" t="s">
         <v>355</v>
       </c>
@@ -13353,7 +13352,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" spans="1:7" ht="12.75">
       <c r="A323" s="4" t="s">
         <v>355</v>
       </c>
@@ -13376,7 +13375,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" spans="1:7" ht="12.75">
       <c r="A324" s="4" t="s">
         <v>355</v>
       </c>
@@ -13399,7 +13398,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" spans="1:7" ht="12.75">
       <c r="A325" s="4" t="s">
         <v>355</v>
       </c>
@@ -13422,7 +13421,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" spans="1:7" ht="12.75">
       <c r="A326" s="4" t="s">
         <v>355</v>
       </c>
@@ -13445,7 +13444,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" spans="1:7" ht="12.75">
       <c r="A327" s="4" t="s">
         <v>355</v>
       </c>
@@ -13468,7 +13467,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" spans="1:7" ht="12.75">
       <c r="A328" s="4" t="s">
         <v>355</v>
       </c>
@@ -13491,7 +13490,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" spans="1:7" ht="12.75">
       <c r="A329" s="4" t="s">
         <v>355</v>
       </c>
@@ -13514,7 +13513,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" spans="1:7" ht="12.75">
       <c r="A330" s="4" t="s">
         <v>355</v>
       </c>
@@ -13537,7 +13536,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" spans="1:7" ht="12.75">
       <c r="A331" s="4" t="s">
         <v>355</v>
       </c>
@@ -13560,7 +13559,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" spans="1:7" ht="12.75">
       <c r="A332" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13583,7 +13582,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" spans="1:7" ht="12.75">
       <c r="A333" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13606,7 +13605,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" spans="1:7" ht="12.75">
       <c r="A334" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13629,7 +13628,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" spans="1:7" ht="12.75">
       <c r="A335" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13652,7 +13651,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" spans="1:7" ht="12.75">
       <c r="A336" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13675,7 +13674,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" spans="1:7" ht="12.75">
       <c r="A337" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13698,7 +13697,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" spans="1:7" ht="12.75">
       <c r="A338" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13721,7 +13720,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" spans="1:7" ht="12.75">
       <c r="A339" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13744,7 +13743,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" spans="1:7" ht="12.75">
       <c r="A340" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13767,7 +13766,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" spans="1:7" ht="12.75">
       <c r="A341" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13790,7 +13789,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" spans="1:7" ht="12.75">
       <c r="A342" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13813,7 +13812,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" spans="1:7" ht="12.75">
       <c r="A343" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13836,7 +13835,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" spans="1:7" ht="12.75">
       <c r="A344" s="4" t="s">
         <v>1455</v>
       </c>
@@ -13859,7 +13858,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" spans="1:7" ht="12.75">
       <c r="A345" s="4" t="s">
         <v>1506</v>
       </c>
@@ -13882,7 +13881,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" spans="1:7" ht="12.75">
       <c r="A346" s="4" t="s">
         <v>1506</v>
       </c>
@@ -13905,7 +13904,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" spans="1:7" ht="12.75">
       <c r="A347" s="4" t="s">
         <v>1506</v>
       </c>
@@ -13928,7 +13927,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" spans="1:7" ht="12.75">
       <c r="A348" s="4" t="s">
         <v>1518</v>
       </c>
@@ -13951,7 +13950,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" spans="1:7" ht="12.75">
       <c r="A349" s="4" t="s">
         <v>1518</v>
       </c>
@@ -13974,7 +13973,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" spans="1:7" ht="12.75">
       <c r="A350" s="4" t="s">
         <v>1518</v>
       </c>
@@ -13997,7 +13996,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" spans="1:7" ht="12.75">
       <c r="A351" s="4" t="s">
         <v>1518</v>
       </c>
@@ -14020,7 +14019,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" spans="1:7" ht="12.75">
       <c r="A352" s="4" t="s">
         <v>1533</v>
       </c>
@@ -14043,7 +14042,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" spans="1:7" ht="12.75">
       <c r="A353" s="4" t="s">
         <v>1533</v>
       </c>
@@ -14066,7 +14065,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" spans="1:7" ht="12.75">
       <c r="A354" s="4" t="s">
         <v>1533</v>
       </c>
@@ -14089,7 +14088,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" spans="1:7" ht="12.75">
       <c r="A355" s="4" t="s">
         <v>1533</v>
       </c>
@@ -14112,7 +14111,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" spans="1:7" ht="12.75">
       <c r="A356" s="4" t="s">
         <v>1533</v>
       </c>
@@ -14135,7 +14134,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" spans="1:7" ht="12.75">
       <c r="A357" s="4" t="s">
         <v>8</v>
       </c>
@@ -14158,7 +14157,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" spans="1:7" ht="12.75">
       <c r="A358" s="4" t="s">
         <v>8</v>
       </c>
@@ -14181,7 +14180,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" spans="1:7" ht="12.75">
       <c r="A359" s="4"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -14190,7 +14189,7 @@
       <c r="F359" s="5"/>
       <c r="G359" s="5"/>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" spans="1:7" ht="12.75">
       <c r="A360" s="1" t="s">
         <v>1560</v>
       </c>
@@ -14201,7 +14200,7 @@
       <c r="F360" s="5"/>
       <c r="G360" s="5"/>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" spans="1:7" ht="12.75">
       <c r="A361" s="5" t="s">
         <v>1561</v>
       </c>
@@ -14224,7 +14223,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" spans="1:7" ht="12.75">
       <c r="A362" s="5" t="s">
         <v>1567</v>
       </c>
@@ -14247,7 +14246,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" spans="1:7" ht="12.75">
       <c r="A363" s="5" t="s">
         <v>1573</v>
       </c>
@@ -14270,7 +14269,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" spans="1:7" ht="12.75">
       <c r="A364" s="5" t="s">
         <v>1579</v>
       </c>
@@ -14293,7 +14292,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" spans="1:7" ht="12.75">
       <c r="A365" s="5" t="s">
         <v>1585</v>
       </c>
@@ -14316,7 +14315,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" spans="1:7" ht="12.75">
       <c r="A366" s="5" t="s">
         <v>312</v>
       </c>
@@ -14339,7 +14338,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" spans="1:7" ht="12.75">
       <c r="A367" s="5" t="s">
         <v>1594</v>
       </c>
@@ -14362,7 +14361,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" spans="1:7" ht="12.75">
       <c r="A368" s="5" t="s">
         <v>1599</v>
       </c>
@@ -14385,7 +14384,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" spans="1:7" ht="12.75">
       <c r="A369" s="5" t="s">
         <v>534</v>
       </c>
@@ -14408,7 +14407,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" spans="1:7" ht="12.75">
       <c r="A370" s="5" t="s">
         <v>534</v>
       </c>
@@ -14431,7 +14430,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" spans="1:7" ht="12.75">
       <c r="A371" s="5" t="s">
         <v>1615</v>
       </c>
@@ -14454,7 +14453,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" spans="1:7" ht="12.75">
       <c r="A372" s="5" t="s">
         <v>1615</v>
       </c>
@@ -14477,7 +14476,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" spans="1:7" ht="12.75">
       <c r="A373" s="5" t="s">
         <v>1623</v>
       </c>
@@ -14500,7 +14499,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" spans="1:7" ht="12.75">
       <c r="A374" s="5" t="s">
         <v>1623</v>
       </c>
@@ -14523,7 +14522,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" spans="1:7" ht="12.75">
       <c r="A375" s="5" t="s">
         <v>1635</v>
       </c>
@@ -14546,7 +14545,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" spans="1:7" ht="12.75">
       <c r="A376" s="5" t="s">
         <v>1641</v>
       </c>
@@ -14569,7 +14568,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" spans="1:7" ht="12.75">
       <c r="A377" s="5" t="s">
         <v>1647</v>
       </c>
@@ -14592,7 +14591,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" spans="1:7" ht="12.75">
       <c r="A378" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14615,7 +14614,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" spans="1:7" ht="12.75">
       <c r="A379" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14638,7 +14637,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" spans="1:7" ht="12.75">
       <c r="A380" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14661,7 +14660,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" spans="1:7" ht="12.75">
       <c r="A381" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14684,7 +14683,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" spans="1:7" ht="12.75">
       <c r="A382" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14707,7 +14706,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" spans="1:7" ht="12.75">
       <c r="A383" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14730,7 +14729,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" spans="1:7" ht="12.75">
       <c r="A384" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14753,7 +14752,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:7" ht="12.75">
       <c r="A385" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14776,7 +14775,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:7" ht="12.75">
       <c r="A386" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14799,7 +14798,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" spans="1:7" ht="12.75">
       <c r="A387" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14822,7 +14821,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" spans="1:7" ht="12.75">
       <c r="A388" s="5" t="s">
         <v>1653</v>
       </c>
@@ -14845,7 +14844,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" spans="1:7" ht="12.75">
       <c r="A389" s="5" t="s">
         <v>1697</v>
       </c>
@@ -14868,7 +14867,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" spans="1:7" ht="12.75">
       <c r="A390" s="5" t="s">
         <v>1697</v>
       </c>
@@ -14891,7 +14890,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" spans="1:7" ht="12.75">
       <c r="A391" s="5" t="s">
         <v>1697</v>
       </c>
@@ -14914,7 +14913,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" spans="1:7" ht="12.75">
       <c r="A392" s="5" t="s">
         <v>1697</v>
       </c>
@@ -14937,7 +14936,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" spans="1:7" ht="12.75">
       <c r="A393" s="5" t="s">
         <v>1716</v>
       </c>
@@ -14960,7 +14959,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" spans="1:7" ht="12.75">
       <c r="A394" s="5" t="s">
         <v>1716</v>
       </c>
@@ -14983,7 +14982,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" spans="1:7" ht="12.75">
       <c r="A395" s="5" t="s">
         <v>1725</v>
       </c>
@@ -15006,7 +15005,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" spans="1:7" ht="12.75">
       <c r="A396" s="5" t="s">
         <v>1731</v>
       </c>
@@ -15029,7 +15028,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" spans="1:7" ht="12.75">
       <c r="A397" s="5" t="s">
         <v>1731</v>
       </c>
@@ -15052,7 +15051,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" spans="1:7" ht="12.75">
       <c r="A398" s="5" t="s">
         <v>1731</v>
       </c>
@@ -15075,7 +15074,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" spans="1:7" ht="12.75">
       <c r="A399" s="5" t="s">
         <v>1747</v>
       </c>
@@ -15098,7 +15097,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" spans="1:7" ht="12.75">
       <c r="A400" s="5" t="s">
         <v>1747</v>
       </c>
@@ -15121,7 +15120,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" spans="1:7" ht="12.75">
       <c r="A401" s="5" t="s">
         <v>20</v>
       </c>
@@ -15144,7 +15143,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" spans="1:7" ht="12.75">
       <c r="A402" s="5" t="s">
         <v>1764</v>
       </c>
@@ -15167,7 +15166,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" spans="1:7" ht="12.75">
       <c r="A403" s="5" t="s">
         <v>1770</v>
       </c>
@@ -15190,7 +15189,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="404" spans="1:7">
+    <row r="404" spans="1:7" ht="12.75">
       <c r="A404" s="5" t="s">
         <v>1770</v>
       </c>
@@ -15213,7 +15212,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
+    <row r="405" spans="1:7" ht="12.75">
       <c r="A405" s="5" t="s">
         <v>1770</v>
       </c>
@@ -15236,7 +15235,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
+    <row r="406" spans="1:7" ht="12.75">
       <c r="A406" s="5" t="s">
         <v>1770</v>
       </c>
@@ -15259,7 +15258,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="407" spans="1:7">
+    <row r="407" spans="1:7" ht="12.75">
       <c r="A407" s="5" t="s">
         <v>1518</v>
       </c>
@@ -15282,7 +15281,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
+    <row r="408" spans="1:7" ht="12.75">
       <c r="A408" s="5" t="s">
         <v>1277</v>
       </c>
@@ -15305,7 +15304,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
+    <row r="409" spans="1:7" ht="12.75">
       <c r="A409" s="5" t="s">
         <v>1533</v>
       </c>
@@ -15328,7 +15327,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
+    <row r="410" spans="1:7" ht="12.75">
       <c r="A410" s="5" t="s">
         <v>1310</v>
       </c>
@@ -15351,7 +15350,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" spans="1:7" ht="12.75">
       <c r="A411" s="5" t="s">
         <v>1802</v>
       </c>
@@ -15374,7 +15373,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" spans="1:7" ht="12.75">
       <c r="A412" s="5" t="s">
         <v>8</v>
       </c>
@@ -15397,7 +15396,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
+    <row r="413" spans="1:7" ht="12.75">
       <c r="A413" s="5" t="s">
         <v>1455</v>
       </c>
@@ -15420,7 +15419,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
+    <row r="414" spans="1:7" ht="12.75">
       <c r="A414" s="5" t="s">
         <v>1814</v>
       </c>
@@ -15443,7 +15442,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" spans="1:7" ht="12.75">
       <c r="A415" s="5" t="s">
         <v>1820</v>
       </c>
@@ -15466,7 +15465,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" spans="1:7" ht="12.75">
       <c r="A416" s="5" t="s">
         <v>1826</v>
       </c>
@@ -15489,7 +15488,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" spans="1:7" ht="12.75">
       <c r="A417" s="5" t="s">
         <v>1647</v>
       </c>
@@ -15512,7 +15511,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" spans="1:7" ht="12.75">
       <c r="A418" s="5" t="s">
         <v>1837</v>
       </c>
@@ -15535,7 +15534,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" spans="1:7" ht="12.75">
       <c r="A419" s="5" t="s">
         <v>1842</v>
       </c>
@@ -15558,7 +15557,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" spans="1:7" ht="12.75">
       <c r="A420" s="5" t="s">
         <v>1847</v>
       </c>
@@ -15581,7 +15580,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" spans="1:7" ht="12.75">
       <c r="A421" s="5" t="s">
         <v>1847</v>
       </c>
@@ -15604,1750 +15603,1750 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" spans="1:7" ht="12.75">
       <c r="A422" s="3"/>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" spans="1:7" ht="12.75">
       <c r="A423" s="3"/>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" spans="1:7" ht="12.75">
       <c r="A424" s="3"/>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" spans="1:7" ht="12.75">
       <c r="A425" s="3"/>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" spans="1:7" ht="12.75">
       <c r="A426" s="3"/>
     </row>
-    <row r="427" spans="1:7">
+    <row r="427" spans="1:7" ht="12.75">
       <c r="A427" s="3"/>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" spans="1:7" ht="12.75">
       <c r="A428" s="3"/>
     </row>
-    <row r="429" spans="1:7">
+    <row r="429" spans="1:7" ht="12.75">
       <c r="A429" s="3"/>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" spans="1:7" ht="12.75">
       <c r="A430" s="3"/>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" spans="1:7" ht="12.75">
       <c r="A431" s="3"/>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" spans="1:7" ht="12.75">
       <c r="A432" s="3"/>
     </row>
-    <row r="433" spans="1:1">
+    <row r="433" spans="1:1" ht="12.75">
       <c r="A433" s="3"/>
     </row>
-    <row r="434" spans="1:1">
+    <row r="434" spans="1:1" ht="12.75">
       <c r="A434" s="3"/>
     </row>
-    <row r="435" spans="1:1">
+    <row r="435" spans="1:1" ht="12.75">
       <c r="A435" s="3"/>
     </row>
-    <row r="436" spans="1:1">
+    <row r="436" spans="1:1" ht="12.75">
       <c r="A436" s="3"/>
     </row>
-    <row r="437" spans="1:1">
+    <row r="437" spans="1:1" ht="12.75">
       <c r="A437" s="3"/>
     </row>
-    <row r="438" spans="1:1">
+    <row r="438" spans="1:1" ht="12.75">
       <c r="A438" s="3"/>
     </row>
-    <row r="439" spans="1:1">
+    <row r="439" spans="1:1" ht="12.75">
       <c r="A439" s="3"/>
     </row>
-    <row r="440" spans="1:1">
+    <row r="440" spans="1:1" ht="12.75">
       <c r="A440" s="3"/>
     </row>
-    <row r="441" spans="1:1">
+    <row r="441" spans="1:1" ht="12.75">
       <c r="A441" s="3"/>
     </row>
-    <row r="442" spans="1:1">
+    <row r="442" spans="1:1" ht="12.75">
       <c r="A442" s="3"/>
     </row>
-    <row r="443" spans="1:1">
+    <row r="443" spans="1:1" ht="12.75">
       <c r="A443" s="3"/>
     </row>
-    <row r="444" spans="1:1">
+    <row r="444" spans="1:1" ht="12.75">
       <c r="A444" s="3"/>
     </row>
-    <row r="445" spans="1:1">
+    <row r="445" spans="1:1" ht="12.75">
       <c r="A445" s="3"/>
     </row>
-    <row r="446" spans="1:1">
+    <row r="446" spans="1:1" ht="12.75">
       <c r="A446" s="3"/>
     </row>
-    <row r="447" spans="1:1">
+    <row r="447" spans="1:1" ht="12.75">
       <c r="A447" s="3"/>
     </row>
-    <row r="448" spans="1:1">
+    <row r="448" spans="1:1" ht="12.75">
       <c r="A448" s="3"/>
     </row>
-    <row r="449" spans="1:1">
+    <row r="449" spans="1:1" ht="12.75">
       <c r="A449" s="3"/>
     </row>
-    <row r="450" spans="1:1">
+    <row r="450" spans="1:1" ht="12.75">
       <c r="A450" s="3"/>
     </row>
-    <row r="451" spans="1:1">
+    <row r="451" spans="1:1" ht="12.75">
       <c r="A451" s="3"/>
     </row>
-    <row r="452" spans="1:1">
+    <row r="452" spans="1:1" ht="12.75">
       <c r="A452" s="3"/>
     </row>
-    <row r="453" spans="1:1">
+    <row r="453" spans="1:1" ht="12.75">
       <c r="A453" s="3"/>
     </row>
-    <row r="454" spans="1:1">
+    <row r="454" spans="1:1" ht="12.75">
       <c r="A454" s="3"/>
     </row>
-    <row r="455" spans="1:1">
+    <row r="455" spans="1:1" ht="12.75">
       <c r="A455" s="3"/>
     </row>
-    <row r="456" spans="1:1">
+    <row r="456" spans="1:1" ht="12.75">
       <c r="A456" s="3"/>
     </row>
-    <row r="457" spans="1:1">
+    <row r="457" spans="1:1" ht="12.75">
       <c r="A457" s="3"/>
     </row>
-    <row r="458" spans="1:1">
+    <row r="458" spans="1:1" ht="12.75">
       <c r="A458" s="3"/>
     </row>
-    <row r="459" spans="1:1">
+    <row r="459" spans="1:1" ht="12.75">
       <c r="A459" s="3"/>
     </row>
-    <row r="460" spans="1:1">
+    <row r="460" spans="1:1" ht="12.75">
       <c r="A460" s="3"/>
     </row>
-    <row r="461" spans="1:1">
+    <row r="461" spans="1:1" ht="12.75">
       <c r="A461" s="3"/>
     </row>
-    <row r="462" spans="1:1">
+    <row r="462" spans="1:1" ht="12.75">
       <c r="A462" s="3"/>
     </row>
-    <row r="463" spans="1:1">
+    <row r="463" spans="1:1" ht="12.75">
       <c r="A463" s="3"/>
     </row>
-    <row r="464" spans="1:1">
+    <row r="464" spans="1:1" ht="12.75">
       <c r="A464" s="3"/>
     </row>
-    <row r="465" spans="1:1">
+    <row r="465" spans="1:1" ht="12.75">
       <c r="A465" s="3"/>
     </row>
-    <row r="466" spans="1:1">
+    <row r="466" spans="1:1" ht="12.75">
       <c r="A466" s="3"/>
     </row>
-    <row r="467" spans="1:1">
+    <row r="467" spans="1:1" ht="12.75">
       <c r="A467" s="3"/>
     </row>
-    <row r="468" spans="1:1">
+    <row r="468" spans="1:1" ht="12.75">
       <c r="A468" s="3"/>
     </row>
-    <row r="469" spans="1:1">
+    <row r="469" spans="1:1" ht="12.75">
       <c r="A469" s="3"/>
     </row>
-    <row r="470" spans="1:1">
+    <row r="470" spans="1:1" ht="12.75">
       <c r="A470" s="3"/>
     </row>
-    <row r="471" spans="1:1">
+    <row r="471" spans="1:1" ht="12.75">
       <c r="A471" s="3"/>
     </row>
-    <row r="472" spans="1:1">
+    <row r="472" spans="1:1" ht="12.75">
       <c r="A472" s="3"/>
     </row>
-    <row r="473" spans="1:1">
+    <row r="473" spans="1:1" ht="12.75">
       <c r="A473" s="3"/>
     </row>
-    <row r="474" spans="1:1">
+    <row r="474" spans="1:1" ht="12.75">
       <c r="A474" s="3"/>
     </row>
-    <row r="475" spans="1:1">
+    <row r="475" spans="1:1" ht="12.75">
       <c r="A475" s="3"/>
     </row>
-    <row r="476" spans="1:1">
+    <row r="476" spans="1:1" ht="12.75">
       <c r="A476" s="3"/>
     </row>
-    <row r="477" spans="1:1">
+    <row r="477" spans="1:1" ht="12.75">
       <c r="A477" s="3"/>
     </row>
-    <row r="478" spans="1:1">
+    <row r="478" spans="1:1" ht="12.75">
       <c r="A478" s="3"/>
     </row>
-    <row r="479" spans="1:1">
+    <row r="479" spans="1:1" ht="12.75">
       <c r="A479" s="3"/>
     </row>
-    <row r="480" spans="1:1">
+    <row r="480" spans="1:1" ht="12.75">
       <c r="A480" s="3"/>
     </row>
-    <row r="481" spans="1:1">
+    <row r="481" spans="1:1" ht="12.75">
       <c r="A481" s="3"/>
     </row>
-    <row r="482" spans="1:1">
+    <row r="482" spans="1:1" ht="12.75">
       <c r="A482" s="3"/>
     </row>
-    <row r="483" spans="1:1">
+    <row r="483" spans="1:1" ht="12.75">
       <c r="A483" s="3"/>
     </row>
-    <row r="484" spans="1:1">
+    <row r="484" spans="1:1" ht="12.75">
       <c r="A484" s="3"/>
     </row>
-    <row r="485" spans="1:1">
+    <row r="485" spans="1:1" ht="12.75">
       <c r="A485" s="3"/>
     </row>
-    <row r="486" spans="1:1">
+    <row r="486" spans="1:1" ht="12.75">
       <c r="A486" s="3"/>
     </row>
-    <row r="487" spans="1:1">
+    <row r="487" spans="1:1" ht="12.75">
       <c r="A487" s="3"/>
     </row>
-    <row r="488" spans="1:1">
+    <row r="488" spans="1:1" ht="12.75">
       <c r="A488" s="3"/>
     </row>
-    <row r="489" spans="1:1">
+    <row r="489" spans="1:1" ht="12.75">
       <c r="A489" s="3"/>
     </row>
-    <row r="490" spans="1:1">
+    <row r="490" spans="1:1" ht="12.75">
       <c r="A490" s="3"/>
     </row>
-    <row r="491" spans="1:1">
+    <row r="491" spans="1:1" ht="12.75">
       <c r="A491" s="3"/>
     </row>
-    <row r="492" spans="1:1">
+    <row r="492" spans="1:1" ht="12.75">
       <c r="A492" s="3"/>
     </row>
-    <row r="493" spans="1:1">
+    <row r="493" spans="1:1" ht="12.75">
       <c r="A493" s="3"/>
     </row>
-    <row r="494" spans="1:1">
+    <row r="494" spans="1:1" ht="12.75">
       <c r="A494" s="3"/>
     </row>
-    <row r="495" spans="1:1">
+    <row r="495" spans="1:1" ht="12.75">
       <c r="A495" s="3"/>
     </row>
-    <row r="496" spans="1:1">
+    <row r="496" spans="1:1" ht="12.75">
       <c r="A496" s="3"/>
     </row>
-    <row r="497" spans="1:1">
+    <row r="497" spans="1:1" ht="12.75">
       <c r="A497" s="3"/>
     </row>
-    <row r="498" spans="1:1">
+    <row r="498" spans="1:1" ht="12.75">
       <c r="A498" s="3"/>
     </row>
-    <row r="499" spans="1:1">
+    <row r="499" spans="1:1" ht="12.75">
       <c r="A499" s="3"/>
     </row>
-    <row r="500" spans="1:1">
+    <row r="500" spans="1:1" ht="12.75">
       <c r="A500" s="3"/>
     </row>
-    <row r="501" spans="1:1">
+    <row r="501" spans="1:1" ht="12.75">
       <c r="A501" s="3"/>
     </row>
-    <row r="502" spans="1:1">
+    <row r="502" spans="1:1" ht="12.75">
       <c r="A502" s="3"/>
     </row>
-    <row r="503" spans="1:1">
+    <row r="503" spans="1:1" ht="12.75">
       <c r="A503" s="3"/>
     </row>
-    <row r="504" spans="1:1">
+    <row r="504" spans="1:1" ht="12.75">
       <c r="A504" s="3"/>
     </row>
-    <row r="505" spans="1:1">
+    <row r="505" spans="1:1" ht="12.75">
       <c r="A505" s="3"/>
     </row>
-    <row r="506" spans="1:1">
+    <row r="506" spans="1:1" ht="12.75">
       <c r="A506" s="3"/>
     </row>
-    <row r="507" spans="1:1">
+    <row r="507" spans="1:1" ht="12.75">
       <c r="A507" s="3"/>
     </row>
-    <row r="508" spans="1:1">
+    <row r="508" spans="1:1" ht="12.75">
       <c r="A508" s="3"/>
     </row>
-    <row r="509" spans="1:1">
+    <row r="509" spans="1:1" ht="12.75">
       <c r="A509" s="3"/>
     </row>
-    <row r="510" spans="1:1">
+    <row r="510" spans="1:1" ht="12.75">
       <c r="A510" s="3"/>
     </row>
-    <row r="511" spans="1:1">
+    <row r="511" spans="1:1" ht="12.75">
       <c r="A511" s="3"/>
     </row>
-    <row r="512" spans="1:1">
+    <row r="512" spans="1:1" ht="12.75">
       <c r="A512" s="3"/>
     </row>
-    <row r="513" spans="1:1">
+    <row r="513" spans="1:1" ht="12.75">
       <c r="A513" s="3"/>
     </row>
-    <row r="514" spans="1:1">
+    <row r="514" spans="1:1" ht="12.75">
       <c r="A514" s="3"/>
     </row>
-    <row r="515" spans="1:1">
+    <row r="515" spans="1:1" ht="12.75">
       <c r="A515" s="3"/>
     </row>
-    <row r="516" spans="1:1">
+    <row r="516" spans="1:1" ht="12.75">
       <c r="A516" s="3"/>
     </row>
-    <row r="517" spans="1:1">
+    <row r="517" spans="1:1" ht="12.75">
       <c r="A517" s="3"/>
     </row>
-    <row r="518" spans="1:1">
+    <row r="518" spans="1:1" ht="12.75">
       <c r="A518" s="3"/>
     </row>
-    <row r="519" spans="1:1">
+    <row r="519" spans="1:1" ht="12.75">
       <c r="A519" s="3"/>
     </row>
-    <row r="520" spans="1:1">
+    <row r="520" spans="1:1" ht="12.75">
       <c r="A520" s="3"/>
     </row>
-    <row r="521" spans="1:1">
+    <row r="521" spans="1:1" ht="12.75">
       <c r="A521" s="3"/>
     </row>
-    <row r="522" spans="1:1">
+    <row r="522" spans="1:1" ht="12.75">
       <c r="A522" s="3"/>
     </row>
-    <row r="523" spans="1:1">
+    <row r="523" spans="1:1" ht="12.75">
       <c r="A523" s="3"/>
     </row>
-    <row r="524" spans="1:1">
+    <row r="524" spans="1:1" ht="12.75">
       <c r="A524" s="3"/>
     </row>
-    <row r="525" spans="1:1">
+    <row r="525" spans="1:1" ht="12.75">
       <c r="A525" s="3"/>
     </row>
-    <row r="526" spans="1:1">
+    <row r="526" spans="1:1" ht="12.75">
       <c r="A526" s="3"/>
     </row>
-    <row r="527" spans="1:1">
+    <row r="527" spans="1:1" ht="12.75">
       <c r="A527" s="3"/>
     </row>
-    <row r="528" spans="1:1">
+    <row r="528" spans="1:1" ht="12.75">
       <c r="A528" s="3"/>
     </row>
-    <row r="529" spans="1:1">
+    <row r="529" spans="1:1" ht="12.75">
       <c r="A529" s="3"/>
     </row>
-    <row r="530" spans="1:1">
+    <row r="530" spans="1:1" ht="12.75">
       <c r="A530" s="3"/>
     </row>
-    <row r="531" spans="1:1">
+    <row r="531" spans="1:1" ht="12.75">
       <c r="A531" s="3"/>
     </row>
-    <row r="532" spans="1:1">
+    <row r="532" spans="1:1" ht="12.75">
       <c r="A532" s="3"/>
     </row>
-    <row r="533" spans="1:1">
+    <row r="533" spans="1:1" ht="12.75">
       <c r="A533" s="3"/>
     </row>
-    <row r="534" spans="1:1">
+    <row r="534" spans="1:1" ht="12.75">
       <c r="A534" s="3"/>
     </row>
-    <row r="535" spans="1:1">
+    <row r="535" spans="1:1" ht="12.75">
       <c r="A535" s="3"/>
     </row>
-    <row r="536" spans="1:1">
+    <row r="536" spans="1:1" ht="12.75">
       <c r="A536" s="3"/>
     </row>
-    <row r="537" spans="1:1">
+    <row r="537" spans="1:1" ht="12.75">
       <c r="A537" s="3"/>
     </row>
-    <row r="538" spans="1:1">
+    <row r="538" spans="1:1" ht="12.75">
       <c r="A538" s="3"/>
     </row>
-    <row r="539" spans="1:1">
+    <row r="539" spans="1:1" ht="12.75">
       <c r="A539" s="3"/>
     </row>
-    <row r="540" spans="1:1">
+    <row r="540" spans="1:1" ht="12.75">
       <c r="A540" s="3"/>
     </row>
-    <row r="541" spans="1:1">
+    <row r="541" spans="1:1" ht="12.75">
       <c r="A541" s="3"/>
     </row>
-    <row r="542" spans="1:1">
+    <row r="542" spans="1:1" ht="12.75">
       <c r="A542" s="3"/>
     </row>
-    <row r="543" spans="1:1">
+    <row r="543" spans="1:1" ht="12.75">
       <c r="A543" s="3"/>
     </row>
-    <row r="544" spans="1:1">
+    <row r="544" spans="1:1" ht="12.75">
       <c r="A544" s="3"/>
     </row>
-    <row r="545" spans="1:1">
+    <row r="545" spans="1:1" ht="12.75">
       <c r="A545" s="3"/>
     </row>
-    <row r="546" spans="1:1">
+    <row r="546" spans="1:1" ht="12.75">
       <c r="A546" s="3"/>
     </row>
-    <row r="547" spans="1:1">
+    <row r="547" spans="1:1" ht="12.75">
       <c r="A547" s="3"/>
     </row>
-    <row r="548" spans="1:1">
+    <row r="548" spans="1:1" ht="12.75">
       <c r="A548" s="3"/>
     </row>
-    <row r="549" spans="1:1">
+    <row r="549" spans="1:1" ht="12.75">
       <c r="A549" s="3"/>
     </row>
-    <row r="550" spans="1:1">
+    <row r="550" spans="1:1" ht="12.75">
       <c r="A550" s="3"/>
     </row>
-    <row r="551" spans="1:1">
+    <row r="551" spans="1:1" ht="12.75">
       <c r="A551" s="3"/>
     </row>
-    <row r="552" spans="1:1">
+    <row r="552" spans="1:1" ht="12.75">
       <c r="A552" s="3"/>
     </row>
-    <row r="553" spans="1:1">
+    <row r="553" spans="1:1" ht="12.75">
       <c r="A553" s="3"/>
     </row>
-    <row r="554" spans="1:1">
+    <row r="554" spans="1:1" ht="12.75">
       <c r="A554" s="3"/>
     </row>
-    <row r="555" spans="1:1">
+    <row r="555" spans="1:1" ht="12.75">
       <c r="A555" s="3"/>
     </row>
-    <row r="556" spans="1:1">
+    <row r="556" spans="1:1" ht="12.75">
       <c r="A556" s="3"/>
     </row>
-    <row r="557" spans="1:1">
+    <row r="557" spans="1:1" ht="12.75">
       <c r="A557" s="3"/>
     </row>
-    <row r="558" spans="1:1">
+    <row r="558" spans="1:1" ht="12.75">
       <c r="A558" s="3"/>
     </row>
-    <row r="559" spans="1:1">
+    <row r="559" spans="1:1" ht="12.75">
       <c r="A559" s="3"/>
     </row>
-    <row r="560" spans="1:1">
+    <row r="560" spans="1:1" ht="12.75">
       <c r="A560" s="3"/>
     </row>
-    <row r="561" spans="1:1">
+    <row r="561" spans="1:1" ht="12.75">
       <c r="A561" s="3"/>
     </row>
-    <row r="562" spans="1:1">
+    <row r="562" spans="1:1" ht="12.75">
       <c r="A562" s="3"/>
     </row>
-    <row r="563" spans="1:1">
+    <row r="563" spans="1:1" ht="12.75">
       <c r="A563" s="3"/>
     </row>
-    <row r="564" spans="1:1">
+    <row r="564" spans="1:1" ht="12.75">
       <c r="A564" s="3"/>
     </row>
-    <row r="565" spans="1:1">
+    <row r="565" spans="1:1" ht="12.75">
       <c r="A565" s="3"/>
     </row>
-    <row r="566" spans="1:1">
+    <row r="566" spans="1:1" ht="12.75">
       <c r="A566" s="3"/>
     </row>
-    <row r="567" spans="1:1">
+    <row r="567" spans="1:1" ht="12.75">
       <c r="A567" s="3"/>
     </row>
-    <row r="568" spans="1:1">
+    <row r="568" spans="1:1" ht="12.75">
       <c r="A568" s="3"/>
     </row>
-    <row r="569" spans="1:1">
+    <row r="569" spans="1:1" ht="12.75">
       <c r="A569" s="3"/>
     </row>
-    <row r="570" spans="1:1">
+    <row r="570" spans="1:1" ht="12.75">
       <c r="A570" s="3"/>
     </row>
-    <row r="571" spans="1:1">
+    <row r="571" spans="1:1" ht="12.75">
       <c r="A571" s="3"/>
     </row>
-    <row r="572" spans="1:1">
+    <row r="572" spans="1:1" ht="12.75">
       <c r="A572" s="3"/>
     </row>
-    <row r="573" spans="1:1">
+    <row r="573" spans="1:1" ht="12.75">
       <c r="A573" s="3"/>
     </row>
-    <row r="574" spans="1:1">
+    <row r="574" spans="1:1" ht="12.75">
       <c r="A574" s="3"/>
     </row>
-    <row r="575" spans="1:1">
+    <row r="575" spans="1:1" ht="12.75">
       <c r="A575" s="3"/>
     </row>
-    <row r="576" spans="1:1">
+    <row r="576" spans="1:1" ht="12.75">
       <c r="A576" s="3"/>
     </row>
-    <row r="577" spans="1:1">
+    <row r="577" spans="1:1" ht="12.75">
       <c r="A577" s="3"/>
     </row>
-    <row r="578" spans="1:1">
+    <row r="578" spans="1:1" ht="12.75">
       <c r="A578" s="3"/>
     </row>
-    <row r="579" spans="1:1">
+    <row r="579" spans="1:1" ht="12.75">
       <c r="A579" s="3"/>
     </row>
-    <row r="580" spans="1:1">
+    <row r="580" spans="1:1" ht="12.75">
       <c r="A580" s="3"/>
     </row>
-    <row r="581" spans="1:1">
+    <row r="581" spans="1:1" ht="12.75">
       <c r="A581" s="3"/>
     </row>
-    <row r="582" spans="1:1">
+    <row r="582" spans="1:1" ht="12.75">
       <c r="A582" s="3"/>
     </row>
-    <row r="583" spans="1:1">
+    <row r="583" spans="1:1" ht="12.75">
       <c r="A583" s="3"/>
     </row>
-    <row r="584" spans="1:1">
+    <row r="584" spans="1:1" ht="12.75">
       <c r="A584" s="3"/>
     </row>
-    <row r="585" spans="1:1">
+    <row r="585" spans="1:1" ht="12.75">
       <c r="A585" s="3"/>
     </row>
-    <row r="586" spans="1:1">
+    <row r="586" spans="1:1" ht="12.75">
       <c r="A586" s="3"/>
     </row>
-    <row r="587" spans="1:1">
+    <row r="587" spans="1:1" ht="12.75">
       <c r="A587" s="3"/>
     </row>
-    <row r="588" spans="1:1">
+    <row r="588" spans="1:1" ht="12.75">
       <c r="A588" s="3"/>
     </row>
-    <row r="589" spans="1:1">
+    <row r="589" spans="1:1" ht="12.75">
       <c r="A589" s="3"/>
     </row>
-    <row r="590" spans="1:1">
+    <row r="590" spans="1:1" ht="12.75">
       <c r="A590" s="3"/>
     </row>
-    <row r="591" spans="1:1">
+    <row r="591" spans="1:1" ht="12.75">
       <c r="A591" s="3"/>
     </row>
-    <row r="592" spans="1:1">
+    <row r="592" spans="1:1" ht="12.75">
       <c r="A592" s="3"/>
     </row>
-    <row r="593" spans="1:1">
+    <row r="593" spans="1:1" ht="12.75">
       <c r="A593" s="3"/>
     </row>
-    <row r="594" spans="1:1">
+    <row r="594" spans="1:1" ht="12.75">
       <c r="A594" s="3"/>
     </row>
-    <row r="595" spans="1:1">
+    <row r="595" spans="1:1" ht="12.75">
       <c r="A595" s="3"/>
     </row>
-    <row r="596" spans="1:1">
+    <row r="596" spans="1:1" ht="12.75">
       <c r="A596" s="3"/>
     </row>
-    <row r="597" spans="1:1">
+    <row r="597" spans="1:1" ht="12.75">
       <c r="A597" s="3"/>
     </row>
-    <row r="598" spans="1:1">
+    <row r="598" spans="1:1" ht="12.75">
       <c r="A598" s="3"/>
     </row>
-    <row r="599" spans="1:1">
+    <row r="599" spans="1:1" ht="12.75">
       <c r="A599" s="3"/>
     </row>
-    <row r="600" spans="1:1">
+    <row r="600" spans="1:1" ht="12.75">
       <c r="A600" s="3"/>
     </row>
-    <row r="601" spans="1:1">
+    <row r="601" spans="1:1" ht="12.75">
       <c r="A601" s="3"/>
     </row>
-    <row r="602" spans="1:1">
+    <row r="602" spans="1:1" ht="12.75">
       <c r="A602" s="3"/>
     </row>
-    <row r="603" spans="1:1">
+    <row r="603" spans="1:1" ht="12.75">
       <c r="A603" s="3"/>
     </row>
-    <row r="604" spans="1:1">
+    <row r="604" spans="1:1" ht="12.75">
       <c r="A604" s="3"/>
     </row>
-    <row r="605" spans="1:1">
+    <row r="605" spans="1:1" ht="12.75">
       <c r="A605" s="3"/>
     </row>
-    <row r="606" spans="1:1">
+    <row r="606" spans="1:1" ht="12.75">
       <c r="A606" s="3"/>
     </row>
-    <row r="607" spans="1:1">
+    <row r="607" spans="1:1" ht="12.75">
       <c r="A607" s="3"/>
     </row>
-    <row r="608" spans="1:1">
+    <row r="608" spans="1:1" ht="12.75">
       <c r="A608" s="3"/>
     </row>
-    <row r="609" spans="1:1">
+    <row r="609" spans="1:1" ht="12.75">
       <c r="A609" s="3"/>
     </row>
-    <row r="610" spans="1:1">
+    <row r="610" spans="1:1" ht="12.75">
       <c r="A610" s="3"/>
     </row>
-    <row r="611" spans="1:1">
+    <row r="611" spans="1:1" ht="12.75">
       <c r="A611" s="3"/>
     </row>
-    <row r="612" spans="1:1">
+    <row r="612" spans="1:1" ht="12.75">
       <c r="A612" s="3"/>
     </row>
-    <row r="613" spans="1:1">
+    <row r="613" spans="1:1" ht="12.75">
       <c r="A613" s="3"/>
     </row>
-    <row r="614" spans="1:1">
+    <row r="614" spans="1:1" ht="12.75">
       <c r="A614" s="3"/>
     </row>
-    <row r="615" spans="1:1">
+    <row r="615" spans="1:1" ht="12.75">
       <c r="A615" s="3"/>
     </row>
-    <row r="616" spans="1:1">
+    <row r="616" spans="1:1" ht="12.75">
       <c r="A616" s="3"/>
     </row>
-    <row r="617" spans="1:1">
+    <row r="617" spans="1:1" ht="12.75">
       <c r="A617" s="3"/>
     </row>
-    <row r="618" spans="1:1">
+    <row r="618" spans="1:1" ht="12.75">
       <c r="A618" s="3"/>
     </row>
-    <row r="619" spans="1:1">
+    <row r="619" spans="1:1" ht="12.75">
       <c r="A619" s="3"/>
     </row>
-    <row r="620" spans="1:1">
+    <row r="620" spans="1:1" ht="12.75">
       <c r="A620" s="3"/>
     </row>
-    <row r="621" spans="1:1">
+    <row r="621" spans="1:1" ht="12.75">
       <c r="A621" s="3"/>
     </row>
-    <row r="622" spans="1:1">
+    <row r="622" spans="1:1" ht="12.75">
       <c r="A622" s="3"/>
     </row>
-    <row r="623" spans="1:1">
+    <row r="623" spans="1:1" ht="12.75">
       <c r="A623" s="3"/>
     </row>
-    <row r="624" spans="1:1">
+    <row r="624" spans="1:1" ht="12.75">
       <c r="A624" s="3"/>
     </row>
-    <row r="625" spans="1:1">
+    <row r="625" spans="1:1" ht="12.75">
       <c r="A625" s="3"/>
     </row>
-    <row r="626" spans="1:1">
+    <row r="626" spans="1:1" ht="12.75">
       <c r="A626" s="3"/>
     </row>
-    <row r="627" spans="1:1">
+    <row r="627" spans="1:1" ht="12.75">
       <c r="A627" s="3"/>
     </row>
-    <row r="628" spans="1:1">
+    <row r="628" spans="1:1" ht="12.75">
       <c r="A628" s="3"/>
     </row>
-    <row r="629" spans="1:1">
+    <row r="629" spans="1:1" ht="12.75">
       <c r="A629" s="3"/>
     </row>
-    <row r="630" spans="1:1">
+    <row r="630" spans="1:1" ht="12.75">
       <c r="A630" s="3"/>
     </row>
-    <row r="631" spans="1:1">
+    <row r="631" spans="1:1" ht="12.75">
       <c r="A631" s="3"/>
     </row>
-    <row r="632" spans="1:1">
+    <row r="632" spans="1:1" ht="12.75">
       <c r="A632" s="3"/>
     </row>
-    <row r="633" spans="1:1">
+    <row r="633" spans="1:1" ht="12.75">
       <c r="A633" s="3"/>
     </row>
-    <row r="634" spans="1:1">
+    <row r="634" spans="1:1" ht="12.75">
       <c r="A634" s="3"/>
     </row>
-    <row r="635" spans="1:1">
+    <row r="635" spans="1:1" ht="12.75">
       <c r="A635" s="3"/>
     </row>
-    <row r="636" spans="1:1">
+    <row r="636" spans="1:1" ht="12.75">
       <c r="A636" s="3"/>
     </row>
-    <row r="637" spans="1:1">
+    <row r="637" spans="1:1" ht="12.75">
       <c r="A637" s="3"/>
     </row>
-    <row r="638" spans="1:1">
+    <row r="638" spans="1:1" ht="12.75">
       <c r="A638" s="3"/>
     </row>
-    <row r="639" spans="1:1">
+    <row r="639" spans="1:1" ht="12.75">
       <c r="A639" s="3"/>
     </row>
-    <row r="640" spans="1:1">
+    <row r="640" spans="1:1" ht="12.75">
       <c r="A640" s="3"/>
     </row>
-    <row r="641" spans="1:1">
+    <row r="641" spans="1:1" ht="12.75">
       <c r="A641" s="3"/>
     </row>
-    <row r="642" spans="1:1">
+    <row r="642" spans="1:1" ht="12.75">
       <c r="A642" s="3"/>
     </row>
-    <row r="643" spans="1:1">
+    <row r="643" spans="1:1" ht="12.75">
       <c r="A643" s="3"/>
     </row>
-    <row r="644" spans="1:1">
+    <row r="644" spans="1:1" ht="12.75">
       <c r="A644" s="3"/>
     </row>
-    <row r="645" spans="1:1">
+    <row r="645" spans="1:1" ht="12.75">
       <c r="A645" s="3"/>
     </row>
-    <row r="646" spans="1:1">
+    <row r="646" spans="1:1" ht="12.75">
       <c r="A646" s="3"/>
     </row>
-    <row r="647" spans="1:1">
+    <row r="647" spans="1:1" ht="12.75">
       <c r="A647" s="3"/>
     </row>
-    <row r="648" spans="1:1">
+    <row r="648" spans="1:1" ht="12.75">
       <c r="A648" s="3"/>
     </row>
-    <row r="649" spans="1:1">
+    <row r="649" spans="1:1" ht="12.75">
       <c r="A649" s="3"/>
     </row>
-    <row r="650" spans="1:1">
+    <row r="650" spans="1:1" ht="12.75">
       <c r="A650" s="3"/>
     </row>
-    <row r="651" spans="1:1">
+    <row r="651" spans="1:1" ht="12.75">
       <c r="A651" s="3"/>
     </row>
-    <row r="652" spans="1:1">
+    <row r="652" spans="1:1" ht="12.75">
       <c r="A652" s="3"/>
     </row>
-    <row r="653" spans="1:1">
+    <row r="653" spans="1:1" ht="12.75">
       <c r="A653" s="3"/>
     </row>
-    <row r="654" spans="1:1">
+    <row r="654" spans="1:1" ht="12.75">
       <c r="A654" s="3"/>
     </row>
-    <row r="655" spans="1:1">
+    <row r="655" spans="1:1" ht="12.75">
       <c r="A655" s="3"/>
     </row>
-    <row r="656" spans="1:1">
+    <row r="656" spans="1:1" ht="12.75">
       <c r="A656" s="3"/>
     </row>
-    <row r="657" spans="1:1">
+    <row r="657" spans="1:1" ht="12.75">
       <c r="A657" s="3"/>
     </row>
-    <row r="658" spans="1:1">
+    <row r="658" spans="1:1" ht="12.75">
       <c r="A658" s="3"/>
     </row>
-    <row r="659" spans="1:1">
+    <row r="659" spans="1:1" ht="12.75">
       <c r="A659" s="3"/>
     </row>
-    <row r="660" spans="1:1">
+    <row r="660" spans="1:1" ht="12.75">
       <c r="A660" s="3"/>
     </row>
-    <row r="661" spans="1:1">
+    <row r="661" spans="1:1" ht="12.75">
       <c r="A661" s="3"/>
     </row>
-    <row r="662" spans="1:1">
+    <row r="662" spans="1:1" ht="12.75">
       <c r="A662" s="3"/>
     </row>
-    <row r="663" spans="1:1">
+    <row r="663" spans="1:1" ht="12.75">
       <c r="A663" s="3"/>
     </row>
-    <row r="664" spans="1:1">
+    <row r="664" spans="1:1" ht="12.75">
       <c r="A664" s="3"/>
     </row>
-    <row r="665" spans="1:1">
+    <row r="665" spans="1:1" ht="12.75">
       <c r="A665" s="3"/>
     </row>
-    <row r="666" spans="1:1">
+    <row r="666" spans="1:1" ht="12.75">
       <c r="A666" s="3"/>
     </row>
-    <row r="667" spans="1:1">
+    <row r="667" spans="1:1" ht="12.75">
       <c r="A667" s="3"/>
     </row>
-    <row r="668" spans="1:1">
+    <row r="668" spans="1:1" ht="12.75">
       <c r="A668" s="3"/>
     </row>
-    <row r="669" spans="1:1">
+    <row r="669" spans="1:1" ht="12.75">
       <c r="A669" s="3"/>
     </row>
-    <row r="670" spans="1:1">
+    <row r="670" spans="1:1" ht="12.75">
       <c r="A670" s="3"/>
     </row>
-    <row r="671" spans="1:1">
+    <row r="671" spans="1:1" ht="12.75">
       <c r="A671" s="3"/>
     </row>
-    <row r="672" spans="1:1">
+    <row r="672" spans="1:1" ht="12.75">
       <c r="A672" s="3"/>
     </row>
-    <row r="673" spans="1:1">
+    <row r="673" spans="1:1" ht="12.75">
       <c r="A673" s="3"/>
     </row>
-    <row r="674" spans="1:1">
+    <row r="674" spans="1:1" ht="12.75">
       <c r="A674" s="3"/>
     </row>
-    <row r="675" spans="1:1">
+    <row r="675" spans="1:1" ht="12.75">
       <c r="A675" s="3"/>
     </row>
-    <row r="676" spans="1:1">
+    <row r="676" spans="1:1" ht="12.75">
       <c r="A676" s="3"/>
     </row>
-    <row r="677" spans="1:1">
+    <row r="677" spans="1:1" ht="12.75">
       <c r="A677" s="3"/>
     </row>
-    <row r="678" spans="1:1">
+    <row r="678" spans="1:1" ht="12.75">
       <c r="A678" s="3"/>
     </row>
-    <row r="679" spans="1:1">
+    <row r="679" spans="1:1" ht="12.75">
       <c r="A679" s="3"/>
     </row>
-    <row r="680" spans="1:1">
+    <row r="680" spans="1:1" ht="12.75">
       <c r="A680" s="3"/>
     </row>
-    <row r="681" spans="1:1">
+    <row r="681" spans="1:1" ht="12.75">
       <c r="A681" s="3"/>
     </row>
-    <row r="682" spans="1:1">
+    <row r="682" spans="1:1" ht="12.75">
       <c r="A682" s="3"/>
     </row>
-    <row r="683" spans="1:1">
+    <row r="683" spans="1:1" ht="12.75">
       <c r="A683" s="3"/>
     </row>
-    <row r="684" spans="1:1">
+    <row r="684" spans="1:1" ht="12.75">
       <c r="A684" s="3"/>
     </row>
-    <row r="685" spans="1:1">
+    <row r="685" spans="1:1" ht="12.75">
       <c r="A685" s="3"/>
     </row>
-    <row r="686" spans="1:1">
+    <row r="686" spans="1:1" ht="12.75">
       <c r="A686" s="3"/>
     </row>
-    <row r="687" spans="1:1">
+    <row r="687" spans="1:1" ht="12.75">
       <c r="A687" s="3"/>
     </row>
-    <row r="688" spans="1:1">
+    <row r="688" spans="1:1" ht="12.75">
       <c r="A688" s="3"/>
     </row>
-    <row r="689" spans="1:1">
+    <row r="689" spans="1:1" ht="12.75">
       <c r="A689" s="3"/>
     </row>
-    <row r="690" spans="1:1">
+    <row r="690" spans="1:1" ht="12.75">
       <c r="A690" s="3"/>
     </row>
-    <row r="691" spans="1:1">
+    <row r="691" spans="1:1" ht="12.75">
       <c r="A691" s="3"/>
     </row>
-    <row r="692" spans="1:1">
+    <row r="692" spans="1:1" ht="12.75">
       <c r="A692" s="3"/>
     </row>
-    <row r="693" spans="1:1">
+    <row r="693" spans="1:1" ht="12.75">
       <c r="A693" s="3"/>
     </row>
-    <row r="694" spans="1:1">
+    <row r="694" spans="1:1" ht="12.75">
       <c r="A694" s="3"/>
     </row>
-    <row r="695" spans="1:1">
+    <row r="695" spans="1:1" ht="12.75">
       <c r="A695" s="3"/>
     </row>
-    <row r="696" spans="1:1">
+    <row r="696" spans="1:1" ht="12.75">
       <c r="A696" s="3"/>
     </row>
-    <row r="697" spans="1:1">
+    <row r="697" spans="1:1" ht="12.75">
       <c r="A697" s="3"/>
     </row>
-    <row r="698" spans="1:1">
+    <row r="698" spans="1:1" ht="12.75">
       <c r="A698" s="3"/>
     </row>
-    <row r="699" spans="1:1">
+    <row r="699" spans="1:1" ht="12.75">
       <c r="A699" s="3"/>
     </row>
-    <row r="700" spans="1:1">
+    <row r="700" spans="1:1" ht="12.75">
       <c r="A700" s="3"/>
     </row>
-    <row r="701" spans="1:1">
+    <row r="701" spans="1:1" ht="12.75">
       <c r="A701" s="3"/>
     </row>
-    <row r="702" spans="1:1">
+    <row r="702" spans="1:1" ht="12.75">
       <c r="A702" s="3"/>
     </row>
-    <row r="703" spans="1:1">
+    <row r="703" spans="1:1" ht="12.75">
       <c r="A703" s="3"/>
     </row>
-    <row r="704" spans="1:1">
+    <row r="704" spans="1:1" ht="12.75">
       <c r="A704" s="3"/>
     </row>
-    <row r="705" spans="1:1">
+    <row r="705" spans="1:1" ht="12.75">
       <c r="A705" s="3"/>
     </row>
-    <row r="706" spans="1:1">
+    <row r="706" spans="1:1" ht="12.75">
       <c r="A706" s="3"/>
     </row>
-    <row r="707" spans="1:1">
+    <row r="707" spans="1:1" ht="12.75">
       <c r="A707" s="3"/>
     </row>
-    <row r="708" spans="1:1">
+    <row r="708" spans="1:1" ht="12.75">
       <c r="A708" s="3"/>
     </row>
-    <row r="709" spans="1:1">
+    <row r="709" spans="1:1" ht="12.75">
       <c r="A709" s="3"/>
     </row>
-    <row r="710" spans="1:1">
+    <row r="710" spans="1:1" ht="12.75">
       <c r="A710" s="3"/>
     </row>
-    <row r="711" spans="1:1">
+    <row r="711" spans="1:1" ht="12.75">
       <c r="A711" s="3"/>
     </row>
-    <row r="712" spans="1:1">
+    <row r="712" spans="1:1" ht="12.75">
       <c r="A712" s="3"/>
     </row>
-    <row r="713" spans="1:1">
+    <row r="713" spans="1:1" ht="12.75">
       <c r="A713" s="3"/>
     </row>
-    <row r="714" spans="1:1">
+    <row r="714" spans="1:1" ht="12.75">
       <c r="A714" s="3"/>
     </row>
-    <row r="715" spans="1:1">
+    <row r="715" spans="1:1" ht="12.75">
       <c r="A715" s="3"/>
     </row>
-    <row r="716" spans="1:1">
+    <row r="716" spans="1:1" ht="12.75">
       <c r="A716" s="3"/>
     </row>
-    <row r="717" spans="1:1">
+    <row r="717" spans="1:1" ht="12.75">
       <c r="A717" s="3"/>
     </row>
-    <row r="718" spans="1:1">
+    <row r="718" spans="1:1" ht="12.75">
       <c r="A718" s="3"/>
     </row>
-    <row r="719" spans="1:1">
+    <row r="719" spans="1:1" ht="12.75">
       <c r="A719" s="3"/>
     </row>
-    <row r="720" spans="1:1">
+    <row r="720" spans="1:1" ht="12.75">
       <c r="A720" s="3"/>
     </row>
-    <row r="721" spans="1:1">
+    <row r="721" spans="1:1" ht="12.75">
       <c r="A721" s="3"/>
     </row>
-    <row r="722" spans="1:1">
+    <row r="722" spans="1:1" ht="12.75">
       <c r="A722" s="3"/>
     </row>
-    <row r="723" spans="1:1">
+    <row r="723" spans="1:1" ht="12.75">
       <c r="A723" s="3"/>
     </row>
-    <row r="724" spans="1:1">
+    <row r="724" spans="1:1" ht="12.75">
       <c r="A724" s="3"/>
     </row>
-    <row r="725" spans="1:1">
+    <row r="725" spans="1:1" ht="12.75">
       <c r="A725" s="3"/>
     </row>
-    <row r="726" spans="1:1">
+    <row r="726" spans="1:1" ht="12.75">
       <c r="A726" s="3"/>
     </row>
-    <row r="727" spans="1:1">
+    <row r="727" spans="1:1" ht="12.75">
       <c r="A727" s="3"/>
     </row>
-    <row r="728" spans="1:1">
+    <row r="728" spans="1:1" ht="12.75">
       <c r="A728" s="3"/>
     </row>
-    <row r="729" spans="1:1">
+    <row r="729" spans="1:1" ht="12.75">
       <c r="A729" s="3"/>
     </row>
-    <row r="730" spans="1:1">
+    <row r="730" spans="1:1" ht="12.75">
       <c r="A730" s="3"/>
     </row>
-    <row r="731" spans="1:1">
+    <row r="731" spans="1:1" ht="12.75">
       <c r="A731" s="3"/>
     </row>
-    <row r="732" spans="1:1">
+    <row r="732" spans="1:1" ht="12.75">
       <c r="A732" s="3"/>
     </row>
-    <row r="733" spans="1:1">
+    <row r="733" spans="1:1" ht="12.75">
       <c r="A733" s="3"/>
     </row>
-    <row r="734" spans="1:1">
+    <row r="734" spans="1:1" ht="12.75">
       <c r="A734" s="3"/>
     </row>
-    <row r="735" spans="1:1">
+    <row r="735" spans="1:1" ht="12.75">
       <c r="A735" s="3"/>
     </row>
-    <row r="736" spans="1:1">
+    <row r="736" spans="1:1" ht="12.75">
       <c r="A736" s="3"/>
     </row>
-    <row r="737" spans="1:1">
+    <row r="737" spans="1:1" ht="12.75">
       <c r="A737" s="3"/>
     </row>
-    <row r="738" spans="1:1">
+    <row r="738" spans="1:1" ht="12.75">
       <c r="A738" s="3"/>
     </row>
-    <row r="739" spans="1:1">
+    <row r="739" spans="1:1" ht="12.75">
       <c r="A739" s="3"/>
     </row>
-    <row r="740" spans="1:1">
+    <row r="740" spans="1:1" ht="12.75">
       <c r="A740" s="3"/>
     </row>
-    <row r="741" spans="1:1">
+    <row r="741" spans="1:1" ht="12.75">
       <c r="A741" s="3"/>
     </row>
-    <row r="742" spans="1:1">
+    <row r="742" spans="1:1" ht="12.75">
       <c r="A742" s="3"/>
     </row>
-    <row r="743" spans="1:1">
+    <row r="743" spans="1:1" ht="12.75">
       <c r="A743" s="3"/>
     </row>
-    <row r="744" spans="1:1">
+    <row r="744" spans="1:1" ht="12.75">
       <c r="A744" s="3"/>
     </row>
-    <row r="745" spans="1:1">
+    <row r="745" spans="1:1" ht="12.75">
       <c r="A745" s="3"/>
     </row>
-    <row r="746" spans="1:1">
+    <row r="746" spans="1:1" ht="12.75">
       <c r="A746" s="3"/>
     </row>
-    <row r="747" spans="1:1">
+    <row r="747" spans="1:1" ht="12.75">
       <c r="A747" s="3"/>
     </row>
-    <row r="748" spans="1:1">
+    <row r="748" spans="1:1" ht="12.75">
       <c r="A748" s="3"/>
     </row>
-    <row r="749" spans="1:1">
+    <row r="749" spans="1:1" ht="12.75">
       <c r="A749" s="3"/>
     </row>
-    <row r="750" spans="1:1">
+    <row r="750" spans="1:1" ht="12.75">
       <c r="A750" s="3"/>
     </row>
-    <row r="751" spans="1:1">
+    <row r="751" spans="1:1" ht="12.75">
       <c r="A751" s="3"/>
     </row>
-    <row r="752" spans="1:1">
+    <row r="752" spans="1:1" ht="12.75">
       <c r="A752" s="3"/>
     </row>
-    <row r="753" spans="1:1">
+    <row r="753" spans="1:1" ht="12.75">
       <c r="A753" s="3"/>
     </row>
-    <row r="754" spans="1:1">
+    <row r="754" spans="1:1" ht="12.75">
       <c r="A754" s="3"/>
     </row>
-    <row r="755" spans="1:1">
+    <row r="755" spans="1:1" ht="12.75">
       <c r="A755" s="3"/>
     </row>
-    <row r="756" spans="1:1">
+    <row r="756" spans="1:1" ht="12.75">
       <c r="A756" s="3"/>
     </row>
-    <row r="757" spans="1:1">
+    <row r="757" spans="1:1" ht="12.75">
       <c r="A757" s="3"/>
     </row>
-    <row r="758" spans="1:1">
+    <row r="758" spans="1:1" ht="12.75">
       <c r="A758" s="3"/>
     </row>
-    <row r="759" spans="1:1">
+    <row r="759" spans="1:1" ht="12.75">
       <c r="A759" s="3"/>
     </row>
-    <row r="760" spans="1:1">
+    <row r="760" spans="1:1" ht="12.75">
       <c r="A760" s="3"/>
     </row>
-    <row r="761" spans="1:1">
+    <row r="761" spans="1:1" ht="12.75">
       <c r="A761" s="3"/>
     </row>
-    <row r="762" spans="1:1">
+    <row r="762" spans="1:1" ht="12.75">
       <c r="A762" s="3"/>
     </row>
-    <row r="763" spans="1:1">
+    <row r="763" spans="1:1" ht="12.75">
       <c r="A763" s="3"/>
     </row>
-    <row r="764" spans="1:1">
+    <row r="764" spans="1:1" ht="12.75">
       <c r="A764" s="3"/>
     </row>
-    <row r="765" spans="1:1">
+    <row r="765" spans="1:1" ht="12.75">
       <c r="A765" s="3"/>
     </row>
-    <row r="766" spans="1:1">
+    <row r="766" spans="1:1" ht="12.75">
       <c r="A766" s="3"/>
     </row>
-    <row r="767" spans="1:1">
+    <row r="767" spans="1:1" ht="12.75">
       <c r="A767" s="3"/>
     </row>
-    <row r="768" spans="1:1">
+    <row r="768" spans="1:1" ht="12.75">
       <c r="A768" s="3"/>
     </row>
-    <row r="769" spans="1:1">
+    <row r="769" spans="1:1" ht="12.75">
       <c r="A769" s="3"/>
     </row>
-    <row r="770" spans="1:1">
+    <row r="770" spans="1:1" ht="12.75">
       <c r="A770" s="3"/>
     </row>
-    <row r="771" spans="1:1">
+    <row r="771" spans="1:1" ht="12.75">
       <c r="A771" s="3"/>
     </row>
-    <row r="772" spans="1:1">
+    <row r="772" spans="1:1" ht="12.75">
       <c r="A772" s="3"/>
     </row>
-    <row r="773" spans="1:1">
+    <row r="773" spans="1:1" ht="12.75">
       <c r="A773" s="3"/>
     </row>
-    <row r="774" spans="1:1">
+    <row r="774" spans="1:1" ht="12.75">
       <c r="A774" s="3"/>
     </row>
-    <row r="775" spans="1:1">
+    <row r="775" spans="1:1" ht="12.75">
       <c r="A775" s="3"/>
     </row>
-    <row r="776" spans="1:1">
+    <row r="776" spans="1:1" ht="12.75">
       <c r="A776" s="3"/>
     </row>
-    <row r="777" spans="1:1">
+    <row r="777" spans="1:1" ht="12.75">
       <c r="A777" s="3"/>
     </row>
-    <row r="778" spans="1:1">
+    <row r="778" spans="1:1" ht="12.75">
       <c r="A778" s="3"/>
     </row>
-    <row r="779" spans="1:1">
+    <row r="779" spans="1:1" ht="12.75">
       <c r="A779" s="3"/>
     </row>
-    <row r="780" spans="1:1">
+    <row r="780" spans="1:1" ht="12.75">
       <c r="A780" s="3"/>
     </row>
-    <row r="781" spans="1:1">
+    <row r="781" spans="1:1" ht="12.75">
       <c r="A781" s="3"/>
     </row>
-    <row r="782" spans="1:1">
+    <row r="782" spans="1:1" ht="12.75">
       <c r="A782" s="3"/>
     </row>
-    <row r="783" spans="1:1">
+    <row r="783" spans="1:1" ht="12.75">
       <c r="A783" s="3"/>
     </row>
-    <row r="784" spans="1:1">
+    <row r="784" spans="1:1" ht="12.75">
       <c r="A784" s="3"/>
     </row>
-    <row r="785" spans="1:1">
+    <row r="785" spans="1:1" ht="12.75">
       <c r="A785" s="3"/>
     </row>
-    <row r="786" spans="1:1">
+    <row r="786" spans="1:1" ht="12.75">
       <c r="A786" s="3"/>
     </row>
-    <row r="787" spans="1:1">
+    <row r="787" spans="1:1" ht="12.75">
       <c r="A787" s="3"/>
     </row>
-    <row r="788" spans="1:1">
+    <row r="788" spans="1:1" ht="12.75">
       <c r="A788" s="3"/>
     </row>
-    <row r="789" spans="1:1">
+    <row r="789" spans="1:1" ht="12.75">
       <c r="A789" s="3"/>
     </row>
-    <row r="790" spans="1:1">
+    <row r="790" spans="1:1" ht="12.75">
       <c r="A790" s="3"/>
     </row>
-    <row r="791" spans="1:1">
+    <row r="791" spans="1:1" ht="12.75">
       <c r="A791" s="3"/>
     </row>
-    <row r="792" spans="1:1">
+    <row r="792" spans="1:1" ht="12.75">
       <c r="A792" s="3"/>
     </row>
-    <row r="793" spans="1:1">
+    <row r="793" spans="1:1" ht="12.75">
       <c r="A793" s="3"/>
     </row>
-    <row r="794" spans="1:1">
+    <row r="794" spans="1:1" ht="12.75">
       <c r="A794" s="3"/>
     </row>
-    <row r="795" spans="1:1">
+    <row r="795" spans="1:1" ht="12.75">
       <c r="A795" s="3"/>
     </row>
-    <row r="796" spans="1:1">
+    <row r="796" spans="1:1" ht="12.75">
       <c r="A796" s="3"/>
     </row>
-    <row r="797" spans="1:1">
+    <row r="797" spans="1:1" ht="12.75">
       <c r="A797" s="3"/>
     </row>
-    <row r="798" spans="1:1">
+    <row r="798" spans="1:1" ht="12.75">
       <c r="A798" s="3"/>
     </row>
-    <row r="799" spans="1:1">
+    <row r="799" spans="1:1" ht="12.75">
       <c r="A799" s="3"/>
     </row>
-    <row r="800" spans="1:1">
+    <row r="800" spans="1:1" ht="12.75">
       <c r="A800" s="3"/>
     </row>
-    <row r="801" spans="1:1">
+    <row r="801" spans="1:1" ht="12.75">
       <c r="A801" s="3"/>
     </row>
-    <row r="802" spans="1:1">
+    <row r="802" spans="1:1" ht="12.75">
       <c r="A802" s="3"/>
     </row>
-    <row r="803" spans="1:1">
+    <row r="803" spans="1:1" ht="12.75">
       <c r="A803" s="3"/>
     </row>
-    <row r="804" spans="1:1">
+    <row r="804" spans="1:1" ht="12.75">
       <c r="A804" s="3"/>
     </row>
-    <row r="805" spans="1:1">
+    <row r="805" spans="1:1" ht="12.75">
       <c r="A805" s="3"/>
     </row>
-    <row r="806" spans="1:1">
+    <row r="806" spans="1:1" ht="12.75">
       <c r="A806" s="3"/>
     </row>
-    <row r="807" spans="1:1">
+    <row r="807" spans="1:1" ht="12.75">
       <c r="A807" s="3"/>
     </row>
-    <row r="808" spans="1:1">
+    <row r="808" spans="1:1" ht="12.75">
       <c r="A808" s="3"/>
     </row>
-    <row r="809" spans="1:1">
+    <row r="809" spans="1:1" ht="12.75">
       <c r="A809" s="3"/>
     </row>
-    <row r="810" spans="1:1">
+    <row r="810" spans="1:1" ht="12.75">
       <c r="A810" s="3"/>
     </row>
-    <row r="811" spans="1:1">
+    <row r="811" spans="1:1" ht="12.75">
       <c r="A811" s="3"/>
     </row>
-    <row r="812" spans="1:1">
+    <row r="812" spans="1:1" ht="12.75">
       <c r="A812" s="3"/>
     </row>
-    <row r="813" spans="1:1">
+    <row r="813" spans="1:1" ht="12.75">
       <c r="A813" s="3"/>
     </row>
-    <row r="814" spans="1:1">
+    <row r="814" spans="1:1" ht="12.75">
       <c r="A814" s="3"/>
     </row>
-    <row r="815" spans="1:1">
+    <row r="815" spans="1:1" ht="12.75">
       <c r="A815" s="3"/>
     </row>
-    <row r="816" spans="1:1">
+    <row r="816" spans="1:1" ht="12.75">
       <c r="A816" s="3"/>
     </row>
-    <row r="817" spans="1:1">
+    <row r="817" spans="1:1" ht="12.75">
       <c r="A817" s="3"/>
     </row>
-    <row r="818" spans="1:1">
+    <row r="818" spans="1:1" ht="12.75">
       <c r="A818" s="3"/>
     </row>
-    <row r="819" spans="1:1">
+    <row r="819" spans="1:1" ht="12.75">
       <c r="A819" s="3"/>
     </row>
-    <row r="820" spans="1:1">
+    <row r="820" spans="1:1" ht="12.75">
       <c r="A820" s="3"/>
     </row>
-    <row r="821" spans="1:1">
+    <row r="821" spans="1:1" ht="12.75">
       <c r="A821" s="3"/>
     </row>
-    <row r="822" spans="1:1">
+    <row r="822" spans="1:1" ht="12.75">
       <c r="A822" s="3"/>
     </row>
-    <row r="823" spans="1:1">
+    <row r="823" spans="1:1" ht="12.75">
       <c r="A823" s="3"/>
     </row>
-    <row r="824" spans="1:1">
+    <row r="824" spans="1:1" ht="12.75">
       <c r="A824" s="3"/>
     </row>
-    <row r="825" spans="1:1">
+    <row r="825" spans="1:1" ht="12.75">
       <c r="A825" s="3"/>
     </row>
-    <row r="826" spans="1:1">
+    <row r="826" spans="1:1" ht="12.75">
       <c r="A826" s="3"/>
     </row>
-    <row r="827" spans="1:1">
+    <row r="827" spans="1:1" ht="12.75">
       <c r="A827" s="3"/>
     </row>
-    <row r="828" spans="1:1">
+    <row r="828" spans="1:1" ht="12.75">
       <c r="A828" s="3"/>
     </row>
-    <row r="829" spans="1:1">
+    <row r="829" spans="1:1" ht="12.75">
       <c r="A829" s="3"/>
     </row>
-    <row r="830" spans="1:1">
+    <row r="830" spans="1:1" ht="12.75">
       <c r="A830" s="3"/>
     </row>
-    <row r="831" spans="1:1">
+    <row r="831" spans="1:1" ht="12.75">
       <c r="A831" s="3"/>
     </row>
-    <row r="832" spans="1:1">
+    <row r="832" spans="1:1" ht="12.75">
       <c r="A832" s="3"/>
     </row>
-    <row r="833" spans="1:1">
+    <row r="833" spans="1:1" ht="12.75">
       <c r="A833" s="3"/>
     </row>
-    <row r="834" spans="1:1">
+    <row r="834" spans="1:1" ht="12.75">
       <c r="A834" s="3"/>
     </row>
-    <row r="835" spans="1:1">
+    <row r="835" spans="1:1" ht="12.75">
       <c r="A835" s="3"/>
     </row>
-    <row r="836" spans="1:1">
+    <row r="836" spans="1:1" ht="12.75">
       <c r="A836" s="3"/>
     </row>
-    <row r="837" spans="1:1">
+    <row r="837" spans="1:1" ht="12.75">
       <c r="A837" s="3"/>
     </row>
-    <row r="838" spans="1:1">
+    <row r="838" spans="1:1" ht="12.75">
       <c r="A838" s="3"/>
     </row>
-    <row r="839" spans="1:1">
+    <row r="839" spans="1:1" ht="12.75">
       <c r="A839" s="3"/>
     </row>
-    <row r="840" spans="1:1">
+    <row r="840" spans="1:1" ht="12.75">
       <c r="A840" s="3"/>
     </row>
-    <row r="841" spans="1:1">
+    <row r="841" spans="1:1" ht="12.75">
       <c r="A841" s="3"/>
     </row>
-    <row r="842" spans="1:1">
+    <row r="842" spans="1:1" ht="12.75">
       <c r="A842" s="3"/>
     </row>
-    <row r="843" spans="1:1">
+    <row r="843" spans="1:1" ht="12.75">
       <c r="A843" s="3"/>
     </row>
-    <row r="844" spans="1:1">
+    <row r="844" spans="1:1" ht="12.75">
       <c r="A844" s="3"/>
     </row>
-    <row r="845" spans="1:1">
+    <row r="845" spans="1:1" ht="12.75">
       <c r="A845" s="3"/>
     </row>
-    <row r="846" spans="1:1">
+    <row r="846" spans="1:1" ht="12.75">
       <c r="A846" s="3"/>
     </row>
-    <row r="847" spans="1:1">
+    <row r="847" spans="1:1" ht="12.75">
       <c r="A847" s="3"/>
     </row>
-    <row r="848" spans="1:1">
+    <row r="848" spans="1:1" ht="12.75">
       <c r="A848" s="3"/>
     </row>
-    <row r="849" spans="1:1">
+    <row r="849" spans="1:1" ht="12.75">
       <c r="A849" s="3"/>
     </row>
-    <row r="850" spans="1:1">
+    <row r="850" spans="1:1" ht="12.75">
       <c r="A850" s="3"/>
     </row>
-    <row r="851" spans="1:1">
+    <row r="851" spans="1:1" ht="12.75">
       <c r="A851" s="3"/>
     </row>
-    <row r="852" spans="1:1">
+    <row r="852" spans="1:1" ht="12.75">
       <c r="A852" s="3"/>
     </row>
-    <row r="853" spans="1:1">
+    <row r="853" spans="1:1" ht="12.75">
       <c r="A853" s="3"/>
     </row>
-    <row r="854" spans="1:1">
+    <row r="854" spans="1:1" ht="12.75">
       <c r="A854" s="3"/>
     </row>
-    <row r="855" spans="1:1">
+    <row r="855" spans="1:1" ht="12.75">
       <c r="A855" s="3"/>
     </row>
-    <row r="856" spans="1:1">
+    <row r="856" spans="1:1" ht="12.75">
       <c r="A856" s="3"/>
     </row>
-    <row r="857" spans="1:1">
+    <row r="857" spans="1:1" ht="12.75">
       <c r="A857" s="3"/>
     </row>
-    <row r="858" spans="1:1">
+    <row r="858" spans="1:1" ht="12.75">
       <c r="A858" s="3"/>
     </row>
-    <row r="859" spans="1:1">
+    <row r="859" spans="1:1" ht="12.75">
       <c r="A859" s="3"/>
     </row>
-    <row r="860" spans="1:1">
+    <row r="860" spans="1:1" ht="12.75">
       <c r="A860" s="3"/>
     </row>
-    <row r="861" spans="1:1">
+    <row r="861" spans="1:1" ht="12.75">
       <c r="A861" s="3"/>
     </row>
-    <row r="862" spans="1:1">
+    <row r="862" spans="1:1" ht="12.75">
       <c r="A862" s="3"/>
     </row>
-    <row r="863" spans="1:1">
+    <row r="863" spans="1:1" ht="12.75">
       <c r="A863" s="3"/>
     </row>
-    <row r="864" spans="1:1">
+    <row r="864" spans="1:1" ht="12.75">
       <c r="A864" s="3"/>
     </row>
-    <row r="865" spans="1:1">
+    <row r="865" spans="1:1" ht="12.75">
       <c r="A865" s="3"/>
     </row>
-    <row r="866" spans="1:1">
+    <row r="866" spans="1:1" ht="12.75">
       <c r="A866" s="3"/>
     </row>
-    <row r="867" spans="1:1">
+    <row r="867" spans="1:1" ht="12.75">
       <c r="A867" s="3"/>
     </row>
-    <row r="868" spans="1:1">
+    <row r="868" spans="1:1" ht="12.75">
       <c r="A868" s="3"/>
     </row>
-    <row r="869" spans="1:1">
+    <row r="869" spans="1:1" ht="12.75">
       <c r="A869" s="3"/>
     </row>
-    <row r="870" spans="1:1">
+    <row r="870" spans="1:1" ht="12.75">
       <c r="A870" s="3"/>
     </row>
-    <row r="871" spans="1:1">
+    <row r="871" spans="1:1" ht="12.75">
       <c r="A871" s="3"/>
     </row>
-    <row r="872" spans="1:1">
+    <row r="872" spans="1:1" ht="12.75">
       <c r="A872" s="3"/>
     </row>
-    <row r="873" spans="1:1">
+    <row r="873" spans="1:1" ht="12.75">
       <c r="A873" s="3"/>
     </row>
-    <row r="874" spans="1:1">
+    <row r="874" spans="1:1" ht="12.75">
       <c r="A874" s="3"/>
     </row>
-    <row r="875" spans="1:1">
+    <row r="875" spans="1:1" ht="12.75">
       <c r="A875" s="3"/>
     </row>
-    <row r="876" spans="1:1">
+    <row r="876" spans="1:1" ht="12.75">
       <c r="A876" s="3"/>
     </row>
-    <row r="877" spans="1:1">
+    <row r="877" spans="1:1" ht="12.75">
       <c r="A877" s="3"/>
     </row>
-    <row r="878" spans="1:1">
+    <row r="878" spans="1:1" ht="12.75">
       <c r="A878" s="3"/>
     </row>
-    <row r="879" spans="1:1">
+    <row r="879" spans="1:1" ht="12.75">
       <c r="A879" s="3"/>
     </row>
-    <row r="880" spans="1:1">
+    <row r="880" spans="1:1" ht="12.75">
       <c r="A880" s="3"/>
     </row>
-    <row r="881" spans="1:1">
+    <row r="881" spans="1:1" ht="12.75">
       <c r="A881" s="3"/>
     </row>
-    <row r="882" spans="1:1">
+    <row r="882" spans="1:1" ht="12.75">
       <c r="A882" s="3"/>
     </row>
-    <row r="883" spans="1:1">
+    <row r="883" spans="1:1" ht="12.75">
       <c r="A883" s="3"/>
     </row>
-    <row r="884" spans="1:1">
+    <row r="884" spans="1:1" ht="12.75">
       <c r="A884" s="3"/>
     </row>
-    <row r="885" spans="1:1">
+    <row r="885" spans="1:1" ht="12.75">
       <c r="A885" s="3"/>
     </row>
-    <row r="886" spans="1:1">
+    <row r="886" spans="1:1" ht="12.75">
       <c r="A886" s="3"/>
     </row>
-    <row r="887" spans="1:1">
+    <row r="887" spans="1:1" ht="12.75">
       <c r="A887" s="3"/>
     </row>
-    <row r="888" spans="1:1">
+    <row r="888" spans="1:1" ht="12.75">
       <c r="A888" s="3"/>
     </row>
-    <row r="889" spans="1:1">
+    <row r="889" spans="1:1" ht="12.75">
       <c r="A889" s="3"/>
     </row>
-    <row r="890" spans="1:1">
+    <row r="890" spans="1:1" ht="12.75">
       <c r="A890" s="3"/>
     </row>
-    <row r="891" spans="1:1">
+    <row r="891" spans="1:1" ht="12.75">
       <c r="A891" s="3"/>
     </row>
-    <row r="892" spans="1:1">
+    <row r="892" spans="1:1" ht="12.75">
       <c r="A892" s="3"/>
     </row>
-    <row r="893" spans="1:1">
+    <row r="893" spans="1:1" ht="12.75">
       <c r="A893" s="3"/>
     </row>
-    <row r="894" spans="1:1">
+    <row r="894" spans="1:1" ht="12.75">
       <c r="A894" s="3"/>
     </row>
-    <row r="895" spans="1:1">
+    <row r="895" spans="1:1" ht="12.75">
       <c r="A895" s="3"/>
     </row>
-    <row r="896" spans="1:1">
+    <row r="896" spans="1:1" ht="12.75">
       <c r="A896" s="3"/>
     </row>
-    <row r="897" spans="1:1">
+    <row r="897" spans="1:1" ht="12.75">
       <c r="A897" s="3"/>
     </row>
-    <row r="898" spans="1:1">
+    <row r="898" spans="1:1" ht="12.75">
       <c r="A898" s="3"/>
     </row>
-    <row r="899" spans="1:1">
+    <row r="899" spans="1:1" ht="12.75">
       <c r="A899" s="3"/>
     </row>
-    <row r="900" spans="1:1">
+    <row r="900" spans="1:1" ht="12.75">
       <c r="A900" s="3"/>
     </row>
-    <row r="901" spans="1:1">
+    <row r="901" spans="1:1" ht="12.75">
       <c r="A901" s="3"/>
     </row>
-    <row r="902" spans="1:1">
+    <row r="902" spans="1:1" ht="12.75">
       <c r="A902" s="3"/>
     </row>
-    <row r="903" spans="1:1">
+    <row r="903" spans="1:1" ht="12.75">
       <c r="A903" s="3"/>
     </row>
-    <row r="904" spans="1:1">
+    <row r="904" spans="1:1" ht="12.75">
       <c r="A904" s="3"/>
     </row>
-    <row r="905" spans="1:1">
+    <row r="905" spans="1:1" ht="12.75">
       <c r="A905" s="3"/>
     </row>
-    <row r="906" spans="1:1">
+    <row r="906" spans="1:1" ht="12.75">
       <c r="A906" s="3"/>
     </row>
-    <row r="907" spans="1:1">
+    <row r="907" spans="1:1" ht="12.75">
       <c r="A907" s="3"/>
     </row>
-    <row r="908" spans="1:1">
+    <row r="908" spans="1:1" ht="12.75">
       <c r="A908" s="3"/>
     </row>
-    <row r="909" spans="1:1">
+    <row r="909" spans="1:1" ht="12.75">
       <c r="A909" s="3"/>
     </row>
-    <row r="910" spans="1:1">
+    <row r="910" spans="1:1" ht="12.75">
       <c r="A910" s="3"/>
     </row>
-    <row r="911" spans="1:1">
+    <row r="911" spans="1:1" ht="12.75">
       <c r="A911" s="3"/>
     </row>
-    <row r="912" spans="1:1">
+    <row r="912" spans="1:1" ht="12.75">
       <c r="A912" s="3"/>
     </row>
-    <row r="913" spans="1:1">
+    <row r="913" spans="1:1" ht="12.75">
       <c r="A913" s="3"/>
     </row>
-    <row r="914" spans="1:1">
+    <row r="914" spans="1:1" ht="12.75">
       <c r="A914" s="3"/>
     </row>
-    <row r="915" spans="1:1">
+    <row r="915" spans="1:1" ht="12.75">
       <c r="A915" s="3"/>
     </row>
-    <row r="916" spans="1:1">
+    <row r="916" spans="1:1" ht="12.75">
       <c r="A916" s="3"/>
     </row>
-    <row r="917" spans="1:1">
+    <row r="917" spans="1:1" ht="12.75">
       <c r="A917" s="3"/>
     </row>
-    <row r="918" spans="1:1">
+    <row r="918" spans="1:1" ht="12.75">
       <c r="A918" s="3"/>
     </row>
-    <row r="919" spans="1:1">
+    <row r="919" spans="1:1" ht="12.75">
       <c r="A919" s="3"/>
     </row>
-    <row r="920" spans="1:1">
+    <row r="920" spans="1:1" ht="12.75">
       <c r="A920" s="3"/>
     </row>
-    <row r="921" spans="1:1">
+    <row r="921" spans="1:1" ht="12.75">
       <c r="A921" s="3"/>
     </row>
-    <row r="922" spans="1:1">
+    <row r="922" spans="1:1" ht="12.75">
       <c r="A922" s="3"/>
     </row>
-    <row r="923" spans="1:1">
+    <row r="923" spans="1:1" ht="12.75">
       <c r="A923" s="3"/>
     </row>
-    <row r="924" spans="1:1">
+    <row r="924" spans="1:1" ht="12.75">
       <c r="A924" s="3"/>
     </row>
-    <row r="925" spans="1:1">
+    <row r="925" spans="1:1" ht="12.75">
       <c r="A925" s="3"/>
     </row>
-    <row r="926" spans="1:1">
+    <row r="926" spans="1:1" ht="12.75">
       <c r="A926" s="3"/>
     </row>
-    <row r="927" spans="1:1">
+    <row r="927" spans="1:1" ht="12.75">
       <c r="A927" s="3"/>
     </row>
-    <row r="928" spans="1:1">
+    <row r="928" spans="1:1" ht="12.75">
       <c r="A928" s="3"/>
     </row>
-    <row r="929" spans="1:1">
+    <row r="929" spans="1:1" ht="12.75">
       <c r="A929" s="3"/>
     </row>
-    <row r="930" spans="1:1">
+    <row r="930" spans="1:1" ht="12.75">
       <c r="A930" s="3"/>
     </row>
-    <row r="931" spans="1:1">
+    <row r="931" spans="1:1" ht="12.75">
       <c r="A931" s="3"/>
     </row>
-    <row r="932" spans="1:1">
+    <row r="932" spans="1:1" ht="12.75">
       <c r="A932" s="3"/>
     </row>
-    <row r="933" spans="1:1">
+    <row r="933" spans="1:1" ht="12.75">
       <c r="A933" s="3"/>
     </row>
-    <row r="934" spans="1:1">
+    <row r="934" spans="1:1" ht="12.75">
       <c r="A934" s="3"/>
     </row>
-    <row r="935" spans="1:1">
+    <row r="935" spans="1:1" ht="12.75">
       <c r="A935" s="3"/>
     </row>
-    <row r="936" spans="1:1">
+    <row r="936" spans="1:1" ht="12.75">
       <c r="A936" s="3"/>
     </row>
-    <row r="937" spans="1:1">
+    <row r="937" spans="1:1" ht="12.75">
       <c r="A937" s="3"/>
     </row>
-    <row r="938" spans="1:1">
+    <row r="938" spans="1:1" ht="12.75">
       <c r="A938" s="3"/>
     </row>
-    <row r="939" spans="1:1">
+    <row r="939" spans="1:1" ht="12.75">
       <c r="A939" s="3"/>
     </row>
-    <row r="940" spans="1:1">
+    <row r="940" spans="1:1" ht="12.75">
       <c r="A940" s="3"/>
     </row>
-    <row r="941" spans="1:1">
+    <row r="941" spans="1:1" ht="12.75">
       <c r="A941" s="3"/>
     </row>
-    <row r="942" spans="1:1">
+    <row r="942" spans="1:1" ht="12.75">
       <c r="A942" s="3"/>
     </row>
-    <row r="943" spans="1:1">
+    <row r="943" spans="1:1" ht="12.75">
       <c r="A943" s="3"/>
     </row>
-    <row r="944" spans="1:1">
+    <row r="944" spans="1:1" ht="12.75">
       <c r="A944" s="3"/>
     </row>
-    <row r="945" spans="1:1">
+    <row r="945" spans="1:1" ht="12.75">
       <c r="A945" s="3"/>
     </row>
-    <row r="946" spans="1:1">
+    <row r="946" spans="1:1" ht="12.75">
       <c r="A946" s="3"/>
     </row>
-    <row r="947" spans="1:1">
+    <row r="947" spans="1:1" ht="12.75">
       <c r="A947" s="3"/>
     </row>
-    <row r="948" spans="1:1">
+    <row r="948" spans="1:1" ht="12.75">
       <c r="A948" s="3"/>
     </row>
-    <row r="949" spans="1:1">
+    <row r="949" spans="1:1" ht="12.75">
       <c r="A949" s="3"/>
     </row>
-    <row r="950" spans="1:1">
+    <row r="950" spans="1:1" ht="12.75">
       <c r="A950" s="3"/>
     </row>
-    <row r="951" spans="1:1">
+    <row r="951" spans="1:1" ht="12.75">
       <c r="A951" s="3"/>
     </row>
-    <row r="952" spans="1:1">
+    <row r="952" spans="1:1" ht="12.75">
       <c r="A952" s="3"/>
     </row>
-    <row r="953" spans="1:1">
+    <row r="953" spans="1:1" ht="12.75">
       <c r="A953" s="3"/>
     </row>
-    <row r="954" spans="1:1">
+    <row r="954" spans="1:1" ht="12.75">
       <c r="A954" s="3"/>
     </row>
-    <row r="955" spans="1:1">
+    <row r="955" spans="1:1" ht="12.75">
       <c r="A955" s="3"/>
     </row>
-    <row r="956" spans="1:1">
+    <row r="956" spans="1:1" ht="12.75">
       <c r="A956" s="3"/>
     </row>
-    <row r="957" spans="1:1">
+    <row r="957" spans="1:1" ht="12.75">
       <c r="A957" s="3"/>
     </row>
-    <row r="958" spans="1:1">
+    <row r="958" spans="1:1" ht="12.75">
       <c r="A958" s="3"/>
     </row>
-    <row r="959" spans="1:1">
+    <row r="959" spans="1:1" ht="12.75">
       <c r="A959" s="3"/>
     </row>
-    <row r="960" spans="1:1">
+    <row r="960" spans="1:1" ht="12.75">
       <c r="A960" s="3"/>
     </row>
-    <row r="961" spans="1:1">
+    <row r="961" spans="1:1" ht="12.75">
       <c r="A961" s="3"/>
     </row>
-    <row r="962" spans="1:1">
+    <row r="962" spans="1:1" ht="12.75">
       <c r="A962" s="3"/>
     </row>
-    <row r="963" spans="1:1">
+    <row r="963" spans="1:1" ht="12.75">
       <c r="A963" s="3"/>
     </row>
-    <row r="964" spans="1:1">
+    <row r="964" spans="1:1" ht="12.75">
       <c r="A964" s="3"/>
     </row>
-    <row r="965" spans="1:1">
+    <row r="965" spans="1:1" ht="12.75">
       <c r="A965" s="3"/>
     </row>
-    <row r="966" spans="1:1">
+    <row r="966" spans="1:1" ht="12.75">
       <c r="A966" s="3"/>
     </row>
-    <row r="967" spans="1:1">
+    <row r="967" spans="1:1" ht="12.75">
       <c r="A967" s="3"/>
     </row>
-    <row r="968" spans="1:1">
+    <row r="968" spans="1:1" ht="12.75">
       <c r="A968" s="3"/>
     </row>
-    <row r="969" spans="1:1">
+    <row r="969" spans="1:1" ht="12.75">
       <c r="A969" s="3"/>
     </row>
-    <row r="970" spans="1:1">
+    <row r="970" spans="1:1" ht="12.75">
       <c r="A970" s="3"/>
     </row>
-    <row r="971" spans="1:1">
+    <row r="971" spans="1:1" ht="12.75">
       <c r="A971" s="3"/>
     </row>
-    <row r="972" spans="1:1">
+    <row r="972" spans="1:1" ht="12.75">
       <c r="A972" s="3"/>
     </row>
-    <row r="973" spans="1:1">
+    <row r="973" spans="1:1" ht="12.75">
       <c r="A973" s="3"/>
     </row>
-    <row r="974" spans="1:1">
+    <row r="974" spans="1:1" ht="12.75">
       <c r="A974" s="3"/>
     </row>
-    <row r="975" spans="1:1">
+    <row r="975" spans="1:1" ht="12.75">
       <c r="A975" s="3"/>
     </row>
-    <row r="976" spans="1:1">
+    <row r="976" spans="1:1" ht="12.75">
       <c r="A976" s="3"/>
     </row>
-    <row r="977" spans="1:1">
+    <row r="977" spans="1:1" ht="12.75">
       <c r="A977" s="3"/>
     </row>
-    <row r="978" spans="1:1">
+    <row r="978" spans="1:1" ht="12.75">
       <c r="A978" s="3"/>
     </row>
-    <row r="979" spans="1:1">
+    <row r="979" spans="1:1" ht="12.75">
       <c r="A979" s="3"/>
     </row>
-    <row r="980" spans="1:1">
+    <row r="980" spans="1:1" ht="12.75">
       <c r="A980" s="3"/>
     </row>
-    <row r="981" spans="1:1">
+    <row r="981" spans="1:1" ht="12.75">
       <c r="A981" s="3"/>
     </row>
-    <row r="982" spans="1:1">
+    <row r="982" spans="1:1" ht="12.75">
       <c r="A982" s="3"/>
     </row>
-    <row r="983" spans="1:1">
+    <row r="983" spans="1:1" ht="12.75">
       <c r="A983" s="3"/>
     </row>
-    <row r="984" spans="1:1">
+    <row r="984" spans="1:1" ht="12.75">
       <c r="A984" s="3"/>
     </row>
-    <row r="985" spans="1:1">
+    <row r="985" spans="1:1" ht="12.75">
       <c r="A985" s="3"/>
     </row>
-    <row r="986" spans="1:1">
+    <row r="986" spans="1:1" ht="12.75">
       <c r="A986" s="3"/>
     </row>
-    <row r="987" spans="1:1">
+    <row r="987" spans="1:1" ht="12.75">
       <c r="A987" s="3"/>
     </row>
-    <row r="988" spans="1:1">
+    <row r="988" spans="1:1" ht="12.75">
       <c r="A988" s="3"/>
     </row>
-    <row r="989" spans="1:1">
+    <row r="989" spans="1:1" ht="12.75">
       <c r="A989" s="3"/>
     </row>
-    <row r="990" spans="1:1">
+    <row r="990" spans="1:1" ht="12.75">
       <c r="A990" s="3"/>
     </row>
-    <row r="991" spans="1:1">
+    <row r="991" spans="1:1" ht="12.75">
       <c r="A991" s="3"/>
     </row>
-    <row r="992" spans="1:1">
+    <row r="992" spans="1:1" ht="12.75">
       <c r="A992" s="3"/>
     </row>
-    <row r="993" spans="1:1">
+    <row r="993" spans="1:1" ht="12.75">
       <c r="A993" s="3"/>
     </row>
-    <row r="994" spans="1:1">
+    <row r="994" spans="1:1" ht="12.75">
       <c r="A994" s="3"/>
     </row>
-    <row r="995" spans="1:1">
+    <row r="995" spans="1:1" ht="12.75">
       <c r="A995" s="3"/>
     </row>
-    <row r="996" spans="1:1">
+    <row r="996" spans="1:1" ht="12.75">
       <c r="A996" s="3"/>
     </row>
-    <row r="997" spans="1:1">
+    <row r="997" spans="1:1" ht="12.75">
       <c r="A997" s="3"/>
     </row>
-    <row r="998" spans="1:1">
+    <row r="998" spans="1:1" ht="12.75">
       <c r="A998" s="3"/>
     </row>
-    <row r="999" spans="1:1">
+    <row r="999" spans="1:1" ht="12.75">
       <c r="A999" s="3"/>
     </row>
-    <row r="1000" spans="1:1">
+    <row r="1000" spans="1:1" ht="12.75">
       <c r="A1000" s="3"/>
     </row>
-    <row r="1001" spans="1:1">
+    <row r="1001" spans="1:1" ht="12.75">
       <c r="A1001" s="3"/>
     </row>
-    <row r="1002" spans="1:1">
+    <row r="1002" spans="1:1" ht="12.75">
       <c r="A1002" s="3"/>
     </row>
-    <row r="1003" spans="1:1">
+    <row r="1003" spans="1:1" ht="12.75">
       <c r="A1003" s="3"/>
     </row>
   </sheetData>
